--- a/stories/arbres/TREE-DIF-005.xlsx
+++ b/stories/arbres/TREE-DIF-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé est au parc, avec papa. Maman s'assoit sur le banc. Un copain parle doucement. Il cherche ses mots. Papa dit : on laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Noé est au parc, avec papa. Maman s'assoit sur le banc. Un copain parle doucement. Il cherche ses mots. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1297,6 +1314,12 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noé est au parc, avec papa. Maman s'assoit sur le banc. Un copain parle doucement. Il cherche ses mots.
+papa|On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1483,6 +1506,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1507,7 +1535,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Noé est encore au parc. Un copain dit : je veux le. Il cherche. Noé laisse le temps. Il attend la fin de la phrase. Papa dit : on écoute jusqu'au bout. On peut jouer ensemble.</t>
+          <t>C'est le matin. Noé est encore au parc. Un Je veux le. Il cherche. Noé laisse le temps. Il attend la fin de la phrase. On écoute jusqu'au bout. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1641,6 +1669,14 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Noé est encore au parc. Un
+enfant-m|Je veux le. Il cherche.
+narrateur|Noé laisse le temps. Il attend la fin de la phrase.
+papa|On écoute jusqu'au bout. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1817,6 +1853,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On laisse le temps ?</t>
         </is>
       </c>
     </row>
@@ -1981,6 +2022,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On laisse le temps. Noé respire. Maman est là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2167,6 +2213,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2191,7 +2242,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans la cuisine. Un copain dit : le ballon est. Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, Noé va dans la cuisine. Un Le ballon est. Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2325,6 +2376,13 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Plus tard, Noé va dans la cuisine. Un
+enfant-m|Le ballon est.
+narrateur|Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2511,6 +2569,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2669,6 +2732,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le matin. Puis la cuisine. Puis le ballon rouge. Le sol est un peu froid. Noé souffle, puis sourit à maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2831,6 +2899,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2989,6 +3062,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Noé s'arrête près de le seau bleu. la cuisine est rangé. La couverture est douce. Noé montre le seau bleu à maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3151,6 +3229,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3309,6 +3392,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Noé se souvient de le matin. Et de la cuisine. Et de le doudou. On range un objet. Noé chuchote : c'est fini. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3471,6 +3559,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3495,7 +3588,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans la cuisine. Un copain dit : le seau est. Noé laisse le temps. Maman dit : je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, Noé va dans la cuisine. Un Le seau est. Noé laisse le temps. Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3629,6 +3722,14 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Plus tard, Noé va dans la cuisine. Un
+enfant-m|Le seau est.
+narrateur|Noé laisse le temps.
+maman|Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3815,6 +3916,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3973,6 +4079,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le matin. Noé s'arrête. Les chaussures font toc toc. Noé caresse le doudou. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4135,6 +4246,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4293,6 +4409,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Noé range le jardin. le seau bleu reste près de le matin. Une tasse cliquette. Noé boit une gorgée d'eau. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4455,6 +4576,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4479,7 +4605,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>le doudou est là. le jardin aussi. le matin reste dans le souvenir. Ça sent le pain chaud. Noé dit : j'ai appris. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Le doudou est là. le jardin aussi. le matin reste dans le souvenir. Ça sent le pain chaud. J'ai appris. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4613,6 +4739,13 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou est là. le jardin aussi. le matin reste dans le souvenir. Ça sent le pain chaud.
+enfant-m|J'ai appris. On laisse le temps. On attend la fin de la phrase. On laisse le temps.
+narrateur|Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4775,6 +4908,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4799,7 +4937,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans la cuisine. Un copain dit : le doudou est. Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, Noé va dans la cuisine. Un Le doudou est. Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4933,6 +5071,13 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Plus tard, Noé va dans la cuisine. Un
+enfant-m|Le doudou est.
+narrateur|Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5119,6 +5264,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5277,6 +5427,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le ballon rouge. la chambre est rangé. le matin est fini. Une pomme brille un peu. Noé range la tasse. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5439,6 +5594,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5597,6 +5757,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le seau bleu. Noé pose la chambre. le matin est derrière. Un ruban reste dans la poche. Noé dit merci à maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5759,6 +5924,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5917,6 +6087,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Noé montre le doudou. Maman a vu le matin. Et la chambre. Il y a des miettes sur la table. Noé raccroche un linge. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6079,6 +6254,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6103,7 +6283,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Noé retrouve le parc. Un copain dit : le bac est. Il s'arrête. Noé laisse le temps. Il attend la fin de la phrase. Maman lui tient la main. On peut jouer ensemble.</t>
+          <t>C'est après la sieste. Noé retrouve le parc. Un Le bac est. Il s'arrête. Noé laisse le temps. Il attend la fin de la phrase. Maman lui tient la main. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6241,6 +6421,13 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Noé retrouve le parc. Un
+enfant-m|Le bac est.
+narrateur|Il s'arrête. Noé laisse le temps. Il attend la fin de la phrase. Maman lui tient la main. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6417,6 +6604,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On finit la phrase à sa place ?</t>
         </is>
       </c>
     </row>
@@ -6581,6 +6773,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On laisse le temps. Noé retient le geste. Maman sourit. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6767,6 +6964,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6791,7 +6993,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans le jardin. Un copain dit : le ballon a. Noé laisse le temps. Maman dit : je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, Noé va dans le jardin. Un Le ballon a. Noé laisse le temps. Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -6925,6 +7127,14 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Plus tard, Noé va dans le jardin. Un
+enfant-m|Le ballon a.
+narrateur|Noé laisse le temps.
+maman|Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7111,6 +7321,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7269,6 +7484,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi après la sieste. Puis la cuisine. Puis le ballon rouge. Un ballon s'immobilise. Noé range encore un peu, près de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7431,6 +7651,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7589,6 +7814,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Noé s'arrête près de le seau bleu. la cuisine est rangé. Un linge sèche à l'air. Noé range après la sieste dans sa tête, comme un souvenir. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7751,6 +7981,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7909,6 +8144,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Noé se souvient de après la sieste. Et de la cuisine. Et de le doudou. Une feuille tombe. Noé écoute maman encore une fois. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8071,6 +8311,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8095,7 +8340,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans le jardin. Un copain dit : le seau a. Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, Noé va dans le jardin. Un Le seau a. Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8229,6 +8474,13 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Plus tard, Noé va dans le jardin. Un
+enfant-m|Le seau a.
+narrateur|Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8415,6 +8667,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8573,6 +8830,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de après la sieste. Noé s'arrête. Un chat miaule une fois. Noé tend le ballon rouge à papa. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8735,6 +8997,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8893,6 +9160,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Noé range le jardin. le seau bleu reste près de après la sieste. On souffle doucement. Noé plie un pull. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9055,6 +9327,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9079,7 +9356,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Un panier est posé sur le banc. Noé répète tout bas le geste. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Un panier est posé sur le banc. Noé répète tout bas le geste. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9213,6 +9490,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Un panier est posé sur le banc. Noé répète tout bas le geste. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9375,6 +9657,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9399,7 +9686,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans le jardin. Un copain dit : le doudou a. Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, Noé va dans le jardin. Un Le doudou a. Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9533,6 +9820,13 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Plus tard, Noé va dans le jardin. Un
+enfant-m|Le doudou a.
+narrateur|Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9719,6 +10013,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9877,6 +10176,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le ballon rouge. la chambre est rangé. après la sieste est fini. La lumière est claire. Papa n'est pas loin. Noé les rejoint. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10039,6 +10343,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10201,6 +10510,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le seau bleu. Noé pose la chambre. après la sieste est derrière. On se tient la main. Noé prend la main de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10363,6 +10677,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10521,6 +10840,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Noé montre le doudou. Maman a vu après la sieste. Et la chambre. On écoute jusqu'au bout. Noé pose sa tête un moment. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10683,6 +11007,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10707,7 +11036,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Le parc devient calme. Un copain dit : je rentre avec. Il cherche le mot. Noé laisse le temps. Il attend la fin de la phrase. Papa sourit. On peut jouer ensemble.</t>
+          <t>C'est le soir. Le parc devient calme. Un Je rentre avec. Il cherche le mot. Noé laisse le temps. Il attend la fin de la phrase. Papa sourit. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10841,6 +11170,13 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le parc devient calme. Un
+enfant-m|Je rentre avec. Il cherche le mot.
+narrateur|Noé laisse le temps. Il attend la fin de la phrase. Papa sourit. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11017,6 +11353,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On attend la fin de la phrase ?</t>
         </is>
       </c>
     </row>
@@ -11181,6 +11522,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On laisse le temps. Noé hoche la tête. On continue, avec maman. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11367,6 +11713,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11391,7 +11742,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans la chambre. Un copain dit : le ballon va. Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, Noé va dans la chambre. Un Le ballon va. Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11525,6 +11876,13 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Plus tard, Noé va dans la chambre. Un
+enfant-m|Le ballon va.
+narrateur|Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11711,6 +12069,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11873,6 +12236,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le soir. Puis la cuisine. Puis le ballon rouge. Une chaussette est encore sablée. Noé essuie ses mains. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12035,6 +12403,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12193,6 +12566,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Noé s'arrête près de le seau bleu. la cuisine est rangé. On dit merci. Noé sourit. Maman sourit aussi. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12355,6 +12733,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12517,6 +12900,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Noé se souvient de le soir. Et de la cuisine. Et de le doudou. Le savon sent bon. Noé serre la main de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12679,6 +13067,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12703,7 +13096,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans la chambre. Un copain dit : le seau va. Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, Noé va dans la chambre. Un Le seau va. Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -12837,6 +13230,13 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Plus tard, Noé va dans la chambre. Un
+enfant-m|Le seau va.
+narrateur|Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13023,6 +13423,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13181,6 +13586,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le soir. Noé s'arrête. On rit un peu. Noé marche près de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13343,6 +13753,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13501,6 +13916,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Noé range le jardin. le seau bleu reste près de le soir. Un vélo passe au loin. Noé pose le jardin à sa place. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13663,6 +14083,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13687,7 +14112,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>le doudou est là. le jardin aussi. le soir reste dans le souvenir. Un crochet tient bien le manteau. Noé ferme le sac. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Le doudou est là. le jardin aussi. le soir reste dans le souvenir. Un crochet tient bien le manteau. Noé ferme le sac. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13821,6 +14246,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou est là. le jardin aussi. le soir reste dans le souvenir. Un crochet tient bien le manteau. Noé ferme le sac. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -13983,6 +14413,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14007,7 +14442,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans la chambre. Un copain dit : le doudou va. Noé laisse le temps. Maman dit : je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, Noé va dans la chambre. Un Le doudou va. Noé laisse le temps. Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14141,6 +14576,14 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Plus tard, Noé va dans la chambre. Un
+enfant-m|Le doudou va.
+narrateur|Noé laisse le temps.
+maman|Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14327,6 +14770,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14485,6 +14933,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le ballon rouge. la chambre est rangé. le soir est fini. Le vent est doux. Noé enfile ses chaussons. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14647,6 +15100,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14805,6 +15263,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le seau bleu. Noé pose la chambre. le soir est derrière. L'eau coule, tout petit bruit. Noé s'assoit près de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -14967,6 +15430,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15125,6 +15593,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Noé montre le doudou. Maman a vu le soir. Et la chambre. Une cloche tinte, tout loin. Noé ferme la porte, tout doux. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15287,6 +15760,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15305,7 +15783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15322,6 +15800,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-005.xlsx
+++ b/stories/arbres/TREE-DIF-005.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1320,6 +1325,11 @@
 papa|On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1511,6 +1521,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1677,6 +1688,11 @@
 papa|On écoute jusqu'au bout. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1860,6 +1876,7 @@
           <t>narrateur|On laisse le temps ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2027,6 +2044,7 @@
           <t>narrateur|Oui. On laisse le temps. Noé respire. Maman est là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2218,6 +2236,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2383,6 +2402,7 @@
 narrateur|Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2574,6 +2594,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2737,6 +2758,7 @@
           <t>narrateur|Noé a choisi le matin. Puis la cuisine. Puis le ballon rouge. Le sol est un peu froid. Noé souffle, puis sourit à maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2904,6 +2926,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3067,6 +3090,7 @@
           <t>narrateur|Noé s'arrête près de le seau bleu. la cuisine est rangé. La couverture est douce. Noé montre le seau bleu à maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3234,6 +3258,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3397,6 +3422,7 @@
           <t>narrateur|Noé se souvient de le matin. Et de la cuisine. Et de le doudou. On range un objet. Noé chuchote : c'est fini. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3564,6 +3590,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3730,6 +3757,7 @@
 maman|Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3921,6 +3949,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4084,6 +4113,7 @@
           <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le matin. Noé s'arrête. Les chaussures font toc toc. Noé caresse le doudou. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4251,6 +4281,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4414,6 +4445,7 @@
           <t>narrateur|Noé range le jardin. le seau bleu reste près de le matin. Une tasse cliquette. Noé boit une gorgée d'eau. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4581,6 +4613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4746,6 +4779,7 @@
 narrateur|Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4913,6 +4947,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5078,6 +5113,7 @@
 narrateur|Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5269,6 +5305,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5432,6 +5469,7 @@
           <t>narrateur|Noé rejoint le ballon rouge. la chambre est rangé. le matin est fini. Une pomme brille un peu. Noé range la tasse. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5599,6 +5637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5762,6 +5801,7 @@
           <t>narrateur|Près de le seau bleu. Noé pose la chambre. le matin est derrière. Un ruban reste dans la poche. Noé dit merci à maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5929,6 +5969,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6092,6 +6133,7 @@
           <t>narrateur|Noé montre le doudou. Maman a vu le matin. Et la chambre. Il y a des miettes sur la table. Noé raccroche un linge. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6259,6 +6301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6428,6 +6471,11 @@
 narrateur|Il s'arrête. Noé laisse le temps. Il attend la fin de la phrase. Maman lui tient la main. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6611,6 +6659,7 @@
           <t>narrateur|On finit la phrase à sa place ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6778,6 +6827,7 @@
           <t>narrateur|Oui. On laisse le temps. Noé retient le geste. Maman sourit. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6969,6 +7019,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7135,6 +7186,7 @@
 maman|Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7326,6 +7378,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7489,6 +7542,7 @@
           <t>narrateur|Noé a choisi après la sieste. Puis la cuisine. Puis le ballon rouge. Un ballon s'immobilise. Noé range encore un peu, près de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7656,6 +7710,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7819,6 +7874,7 @@
           <t>narrateur|Noé s'arrête près de le seau bleu. la cuisine est rangé. Un linge sèche à l'air. Noé range après la sieste dans sa tête, comme un souvenir. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7986,6 +8042,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8149,6 +8206,7 @@
           <t>narrateur|Noé se souvient de après la sieste. Et de la cuisine. Et de le doudou. Une feuille tombe. Noé écoute maman encore une fois. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8316,6 +8374,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8481,6 +8540,7 @@
 narrateur|Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8672,6 +8732,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8835,6 +8896,7 @@
           <t>narrateur|Avec le ballon rouge. Après le jardin. Près de après la sieste. Noé s'arrête. Un chat miaule une fois. Noé tend le ballon rouge à papa. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9002,6 +9064,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9165,6 +9228,7 @@
           <t>narrateur|Noé range le jardin. le seau bleu reste près de après la sieste. On souffle doucement. Noé plie un pull. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9332,6 +9396,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9495,6 +9560,7 @@
           <t>narrateur|Le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Un panier est posé sur le banc. Noé répète tout bas le geste. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9662,6 +9728,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9827,6 +9894,7 @@
 narrateur|Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10018,6 +10086,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10181,6 +10250,7 @@
           <t>narrateur|Noé rejoint le ballon rouge. la chambre est rangé. après la sieste est fini. La lumière est claire. Papa n'est pas loin. Noé les rejoint. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10348,6 +10418,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10515,6 +10586,7 @@
           <t>narrateur|Près de le seau bleu. Noé pose la chambre. après la sieste est derrière. On se tient la main. Noé prend la main de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10682,6 +10754,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10845,6 +10918,7 @@
           <t>narrateur|Noé montre le doudou. Maman a vu après la sieste. Et la chambre. On écoute jusqu'au bout. Noé pose sa tête un moment. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11012,6 +11086,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11177,6 +11252,11 @@
 narrateur|Noé laisse le temps. Il attend la fin de la phrase. Papa sourit. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11360,6 +11440,7 @@
           <t>narrateur|On attend la fin de la phrase ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11527,6 +11608,7 @@
           <t>narrateur|Oui. On laisse le temps. Noé hoche la tête. On continue, avec maman. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11718,6 +11800,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11883,6 +11966,7 @@
 narrateur|Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12074,6 +12158,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12241,6 +12326,7 @@
           <t>narrateur|Noé a choisi le soir. Puis la cuisine. Puis le ballon rouge. Une chaussette est encore sablée. Noé essuie ses mains. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12408,6 +12494,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12571,6 +12658,7 @@
           <t>narrateur|Noé s'arrête près de le seau bleu. la cuisine est rangé. On dit merci. Noé sourit. Maman sourit aussi. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12738,6 +12826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12905,6 +12994,7 @@
           <t>narrateur|Noé se souvient de le soir. Et de la cuisine. Et de le doudou. Le savon sent bon. Noé serre la main de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13072,6 +13162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13237,6 +13328,7 @@
 narrateur|Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13428,6 +13520,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13591,6 +13684,7 @@
           <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le soir. Noé s'arrête. On rit un peu. Noé marche près de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13758,6 +13852,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13921,6 +14016,7 @@
           <t>narrateur|Noé range le jardin. le seau bleu reste près de le soir. Un vélo passe au loin. Noé pose le jardin à sa place. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14088,6 +14184,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14251,6 +14348,7 @@
           <t>narrateur|Le doudou est là. le jardin aussi. le soir reste dans le souvenir. Un crochet tient bien le manteau. Noé ferme le sac. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14418,6 +14516,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14584,6 +14683,7 @@
 maman|Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14775,6 +14875,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14938,6 +15039,7 @@
           <t>narrateur|Noé rejoint le ballon rouge. la chambre est rangé. le soir est fini. Le vent est doux. Noé enfile ses chaussons. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15105,6 +15207,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15268,6 +15371,7 @@
           <t>narrateur|Près de le seau bleu. Noé pose la chambre. le soir est derrière. L'eau coule, tout petit bruit. Noé s'assoit près de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15435,6 +15539,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15598,6 +15703,7 @@
           <t>narrateur|Noé montre le doudou. Maman a vu le soir. Et la chambre. Une cloche tinte, tout loin. Noé ferme la porte, tout doux. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15765,6 +15871,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15783,7 +15890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15807,6 +15914,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15821,7 +15942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16008,6 +16129,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-005.xlsx
+++ b/stories/arbres/TREE-DIF-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Laisser le temps à l'autre de finir sa phrase — au parc</t>
+          <t>Le sable du toboggan et la phrase d'Aniss</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DIF.COR.001</t>
+          <t>DIF.PAR.001</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le sable colle au toboggan. Aniss cherche ses mots. Victorino attend la fin de la phrase. Le ballon, le seau, le doudou. Les phrases se finissent, tout doucement.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé est au parc, avec papa. Maman s'assoit sur le banc. Un copain parle doucement. Il cherche ses mots. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Le toboggan a encore du sable. Un grain brille, tout chaud. Une feuille tourne dans une flaque. Le banc du parc est tiède. Ça sent l'herbe coupée. Un oiseau saute près du seau. Papa noue un lacet, tout doux. Maman pose le panier sur le banc. Tu sens l'herbe, Victorino ? Elle sent vert, papa. Le banc est encore chaud. En ce moment, Aniss arrive. Il parle tout doucement. Il cherche déjà un mot. Je veux le... Aniss s'arrête. Victorino ouvre la bouche. On laisse le temps. On attend la fin de la phrase. Victorino referme la bouche. Il pose les mains sur le banc. Je veux le seau. Bravo, Victorino. Tu as su attendre. On peut jouer ensemble. Le seau bleu reste sur le sable.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1321,8 +1333,32 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noé est au parc, avec papa. Maman s'assoit sur le banc. Un copain parle doucement. Il cherche ses mots.
-papa|On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>narrateur|Le toboggan a encore du sable.
+narrateur|Un grain brille, tout chaud.
+narrateur|Une feuille tourne dans une flaque.
+narrateur|Le banc du parc est tiède.
+narrateur|Ça sent l'herbe coupée.
+narrateur|Un oiseau saute près du seau.
+narrateur|Papa noue un lacet, tout doux.
+narrateur|Maman pose le panier sur le banc.
+papa|Tu sens l'herbe, Victorino ?
+enfant-m|Elle sent vert, papa.
+maman|Le banc est encore chaud.
+narrateur|En ce moment, Aniss arrive.
+narrateur|Il parle tout doucement.
+narrateur|Il cherche déjà un mot.
+copain|Je veux le...
+narrateur|Aniss s'arrête.
+narrateur|Victorino ouvre la bouche.
+papa|On laisse le temps.
+papa|On attend la fin de la phrase.
+narrateur|Victorino referme la bouche.
+narrateur|Il pose les mains sur le banc.
+copain|Je veux le seau.
+maman|Bravo, Victorino.
+maman|Tu as su attendre.
+papa|On peut jouer ensemble.
+narrateur|Le seau bleu reste sur le sable.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1354,7 +1390,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On laisse le temps.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1554,9 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On laisse le temps.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Noé est encore au parc. Un Je veux le. Il cherche. Noé laisse le temps. Il attend la fin de la phrase. On écoute jusqu'au bout. On peut jouer ensemble.</t>
+          <t>La rosée brille encore sur le banc. Le toboggan a un grain de sable. Ça sent l'herbe, tout frais. Le parc se réveille, Victorino. Oui, papa. Aniss s'approche du bac. Je veux le... Aniss cherche le mot. Victorino ouvre la bouche. On laisse le temps. On attend la fin de la phrase. Victorino referme la bouche. Il pose les mains sur le banc. Je veux le bac. Bravo, Victorino. Tu as su attendre. On peut jouer ensemble. Le bac à sable est encore frais.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1682,10 +1720,24 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Noé est encore au parc. Un
-enfant-m|Je veux le. Il cherche.
-narrateur|Noé laisse le temps. Il attend la fin de la phrase.
-papa|On écoute jusqu'au bout. On peut jouer ensemble.</t>
+          <t>narrateur|La rosée brille encore sur le banc.
+narrateur|Le toboggan a un grain de sable.
+narrateur|Ça sent l'herbe, tout frais.
+papa|Le parc se réveille, Victorino.
+enfant-m|Oui, papa.
+narrateur|Aniss s'approche du bac.
+copain|Je veux le...
+narrateur|Aniss cherche le mot.
+narrateur|Victorino ouvre la bouche.
+papa|On laisse le temps.
+papa|On attend la fin de la phrase.
+narrateur|Victorino referme la bouche.
+narrateur|Il pose les mains sur le banc.
+copain|Je veux le bac.
+maman|Bravo, Victorino.
+maman|Tu as su attendre.
+papa|On peut jouer ensemble.
+narrateur|Le bac à sable est encore frais.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1717,7 +1769,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On laisse le temps ?</t>
+          <t>Aniss cherche un mot. On laisse le temps ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1873,7 +1925,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|On laisse le temps ?</t>
+          <t>narrateur|Aniss cherche un mot.
+papa|On laisse le temps ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1901,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On laisse le temps. Noé respire. Maman est là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Oui. On laisse le temps. On attend la fin de la phrase. Victorino souffle un peu. J'attends. Bravo, Victorino. C'est du bon travail. Le banc reste tiède sous les mains.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2041,7 +2094,14 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On laisse le temps. Noé respire. Maman est là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>maman|Oui.
+maman|On laisse le temps.
+papa|On attend la fin de la phrase.
+narrateur|Victorino souffle un peu.
+enfant-m|J'attends.
+papa|Bravo, Victorino.
+papa|C'est du bon travail.
+narrateur|Le banc reste tiède sous les mains.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2069,7 +2129,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Trois coins de la maison attendent. La cuisine, le jardin, ou la chambre ? On attend la fin de la phrase.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2233,7 +2293,9 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Trois coins de la maison attendent.
+maman|La cuisine, le jardin, ou la chambre ?
+papa|On attend la fin de la phrase.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2261,7 +2323,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans la cuisine. Un Le ballon est. Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, la cuisine sent le pain. La nappe est un peu rêche. Une miette dort près du sel. On se lave les mains ? Oui, maman. Le pain est... Aniss s'arrête. Victorino attend. On laisse le temps. On attend la fin de la phrase. Le pain est tiède. Bravo, Victorino. Tu as su attendre. L'eau coule, tout petit bruit. Un rayon jaune touche le saladier. On laisse le temps. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2397,9 +2459,23 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, Noé va dans la cuisine. Un
-enfant-m|Le ballon est.
-narrateur|Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>narrateur|Plus tard, la cuisine sent le pain.
+narrateur|La nappe est un peu rêche.
+narrateur|Une miette dort près du sel.
+maman|On se lave les mains ?
+enfant-m|Oui, maman.
+copain|Le pain est...
+narrateur|Aniss s'arrête.
+narrateur|Victorino attend.
+papa|On laisse le temps.
+papa|On attend la fin de la phrase.
+copain|Le pain est tiède.
+maman|Bravo, Victorino.
+maman|Tu as su attendre.
+narrateur|L'eau coule, tout petit bruit.
+narrateur|Un rayon jaune touche le saladier.
+maman|On laisse le temps.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2427,7 +2503,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois objets attendent, tout proches. Le ballon rouge, le seau bleu, ou le doudou ? On laisse le temps.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2591,7 +2667,9 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois objets attendent, tout proches.
+papa|Le ballon rouge, le seau bleu, ou le doudou ?
+maman|On laisse le temps.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2619,7 +2697,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le matin. Puis la cuisine. Puis le ballon rouge. Le sol est un peu froid. Noé souffle, puis sourit à maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le ballon rouge. Le caoutchouc est un peu rêche. Le ballon est... Aniss cherche. Victorino attend. On laisse le temps. Le ballon est rouge. Bravo. Tu as attendu la fin. Il est rouge, oui. On peut jouer ensemble. Le ballon roule près du saladier froid. On est encore dans la cuisine. C'est encore le matin. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2755,7 +2833,24 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le matin. Puis la cuisine. Puis le ballon rouge. Le sol est un peu froid. Noé souffle, puis sourit à maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le ballon rouge.
+narrateur|Le caoutchouc est un peu rêche.
+copain|Le ballon est...
+narrateur|Aniss cherche.
+narrateur|Victorino attend.
+papa|On laisse le temps.
+copain|Le ballon est rouge.
+maman|Bravo.
+maman|Tu as attendu la fin.
+enfant-m|Il est rouge, oui.
+papa|On peut jouer ensemble.
+narrateur|Le ballon roule près du saladier froid.
+narrateur|On est encore dans la cuisine.
+narrateur|C'est encore le matin.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2783,7 +2878,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le matin. Il a joué dans la cuisine. Aniss a fini sa phrase, près du ballon rouge. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2923,7 +3018,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le matin.
+narrateur|Il a joué dans la cuisine.
+narrateur|Aniss a fini sa phrase, près du ballon rouge.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2951,7 +3055,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Noé s'arrête près de le seau bleu. la cuisine est rangé. La couverture est douce. Noé montre le seau bleu à maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino pose le seau bleu. Le plastique sonne, tout creux. Le seau est... Aniss s'arrête. Victorino attend la fin. On laisse le temps. Le seau est bleu. Bravo, Victorino. Tu as su attendre. Il est bleu. On peut jouer ensemble. Le seau bleu sonne près de l'évier. On est encore dans la cuisine. C'est encore le matin. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3087,7 +3191,24 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Noé s'arrête près de le seau bleu. la cuisine est rangé. La couverture est douce. Noé montre le seau bleu à maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino pose le seau bleu.
+narrateur|Le plastique sonne, tout creux.
+copain|Le seau est...
+narrateur|Aniss s'arrête.
+narrateur|Victorino attend la fin.
+maman|On laisse le temps.
+copain|Le seau est bleu.
+papa|Bravo, Victorino.
+papa|Tu as su attendre.
+enfant-m|Il est bleu.
+maman|On peut jouer ensemble.
+narrateur|Le seau bleu sonne près de l'évier.
+narrateur|On est encore dans la cuisine.
+narrateur|C'est encore le matin.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3115,7 +3236,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le matin. Il a joué dans la cuisine. Aniss a fini sa phrase, près du seau bleu. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3255,7 +3376,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le matin.
+narrateur|Il a joué dans la cuisine.
+narrateur|Aniss a fini sa phrase, près du seau bleu.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3283,7 +3413,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Noé se souvient de le matin. Et de la cuisine. Et de le doudou. On range un objet. Noé chuchote : c'est fini. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le doudou. Le tissu est doux, un peu lourd. Le doudou va... Aniss cherche le mot. Victorino attend. On attend la fin de la phrase. Le doudou va venir. Bravo. Tu as laissé le temps. Il vient. On peut jouer ensemble. Le doudou sent encore le pain chaud. On est encore dans la cuisine. C'est encore le matin. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3419,7 +3549,24 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Noé se souvient de le matin. Et de la cuisine. Et de le doudou. On range un objet. Noé chuchote : c'est fini. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le doudou.
+narrateur|Le tissu est doux, un peu lourd.
+copain|Le doudou va...
+narrateur|Aniss cherche le mot.
+narrateur|Victorino attend.
+papa|On attend la fin de la phrase.
+copain|Le doudou va venir.
+maman|Bravo.
+maman|Tu as laissé le temps.
+enfant-m|Il vient.
+papa|On peut jouer ensemble.
+narrateur|Le doudou sent encore le pain chaud.
+narrateur|On est encore dans la cuisine.
+narrateur|C'est encore le matin.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3447,7 +3594,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le matin. Il a joué dans la cuisine. Aniss a fini sa phrase, près du doudou. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3587,7 +3734,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le matin.
+narrateur|Il a joué dans la cuisine.
+narrateur|Aniss a fini sa phrase, près du doudou.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3615,7 +3771,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans la cuisine. Un Le seau est. Noé laisse le temps. Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, le jardin a de l'herbe mouillée. Une feuille colle à la chaussette. Le banc de bois reste froid. Tu sens l'herbe ? Elle sent vert. Le ballon a... Aniss cherche. Victorino attend la fin. On laisse le temps. On attend la fin de la phrase. Le ballon a de l'herbe. Bravo. Tu as laissé le temps. Une goutte glisse sur le ballon. La rosée brille encore sur l'herbe. On laisse le temps. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3751,10 +3907,23 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, Noé va dans la cuisine. Un
-enfant-m|Le seau est.
-narrateur|Noé laisse le temps.
-maman|Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>narrateur|Plus tard, le jardin a de l'herbe mouillée.
+narrateur|Une feuille colle à la chaussette.
+narrateur|Le banc de bois reste froid.
+papa|Tu sens l'herbe ?
+enfant-m|Elle sent vert.
+copain|Le ballon a...
+narrateur|Aniss cherche.
+narrateur|Victorino attend la fin.
+maman|On laisse le temps.
+maman|On attend la fin de la phrase.
+copain|Le ballon a de l'herbe.
+papa|Bravo.
+papa|Tu as laissé le temps.
+narrateur|Une goutte glisse sur le ballon.
+narrateur|La rosée brille encore sur l'herbe.
+maman|On laisse le temps.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3782,7 +3951,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois objets attendent, tout proches. Le ballon rouge, le seau bleu, ou le doudou ? On laisse le temps.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3946,7 +4115,9 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois objets attendent, tout proches.
+papa|Le ballon rouge, le seau bleu, ou le doudou ?
+maman|On laisse le temps.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3974,7 +4145,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec le ballon rouge. Après le jardin. Près de le matin. Noé s'arrête. Les chaussures font toc toc. Noé caresse le doudou. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le ballon rouge. Le caoutchouc est un peu rêche. Le ballon est... Aniss cherche. Victorino attend. On laisse le temps. Le ballon est rouge. Bravo. Tu as attendu la fin. Il est rouge, oui. On peut jouer ensemble. Le ballon a un grain d'herbe collé. On est encore dans le jardin. C'est encore le matin. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4110,7 +4281,24 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le matin. Noé s'arrête. Les chaussures font toc toc. Noé caresse le doudou. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le ballon rouge.
+narrateur|Le caoutchouc est un peu rêche.
+copain|Le ballon est...
+narrateur|Aniss cherche.
+narrateur|Victorino attend.
+papa|On laisse le temps.
+copain|Le ballon est rouge.
+maman|Bravo.
+maman|Tu as attendu la fin.
+enfant-m|Il est rouge, oui.
+papa|On peut jouer ensemble.
+narrateur|Le ballon a un grain d'herbe collé.
+narrateur|On est encore dans le jardin.
+narrateur|C'est encore le matin.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4138,7 +4326,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le matin. Il a joué dans le jardin. Aniss a fini sa phrase, près du ballon rouge. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4278,7 +4466,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le matin.
+narrateur|Il a joué dans le jardin.
+narrateur|Aniss a fini sa phrase, près du ballon rouge.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4306,7 +4503,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Noé range le jardin. le seau bleu reste près de le matin. Une tasse cliquette. Noé boit une gorgée d'eau. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino pose le seau bleu. Le plastique sonne, tout creux. Le seau est... Aniss s'arrête. Victorino attend la fin. On laisse le temps. Le seau est bleu. Bravo, Victorino. Tu as su attendre. Il est bleu. On peut jouer ensemble. Le seau ramasse une feuille mouillée. On est encore dans le jardin. C'est encore le matin. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4442,7 +4639,24 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Noé range le jardin. le seau bleu reste près de le matin. Une tasse cliquette. Noé boit une gorgée d'eau. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino pose le seau bleu.
+narrateur|Le plastique sonne, tout creux.
+copain|Le seau est...
+narrateur|Aniss s'arrête.
+narrateur|Victorino attend la fin.
+maman|On laisse le temps.
+copain|Le seau est bleu.
+papa|Bravo, Victorino.
+papa|Tu as su attendre.
+enfant-m|Il est bleu.
+maman|On peut jouer ensemble.
+narrateur|Le seau ramasse une feuille mouillée.
+narrateur|On est encore dans le jardin.
+narrateur|C'est encore le matin.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4470,7 +4684,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le matin. Il a joué dans le jardin. Aniss a fini sa phrase, près du seau bleu. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4610,7 +4824,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le matin.
+narrateur|Il a joué dans le jardin.
+narrateur|Aniss a fini sa phrase, près du seau bleu.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4638,7 +4861,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le doudou est là. le jardin aussi. le matin reste dans le souvenir. Ça sent le pain chaud. J'ai appris. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le doudou. Le tissu est doux, un peu lourd. Le doudou va... Aniss cherche le mot. Victorino attend. On attend la fin de la phrase. Le doudou va venir. Bravo. Tu as laissé le temps. Il vient. On peut jouer ensemble. Le doudou a un brin d'herbe, tout vert. On est encore dans le jardin. C'est encore le matin. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4774,9 +4997,24 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Le doudou est là. le jardin aussi. le matin reste dans le souvenir. Ça sent le pain chaud.
-enfant-m|J'ai appris. On laisse le temps. On attend la fin de la phrase. On laisse le temps.
-narrateur|Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le doudou.
+narrateur|Le tissu est doux, un peu lourd.
+copain|Le doudou va...
+narrateur|Aniss cherche le mot.
+narrateur|Victorino attend.
+papa|On attend la fin de la phrase.
+copain|Le doudou va venir.
+maman|Bravo.
+maman|Tu as laissé le temps.
+enfant-m|Il vient.
+papa|On peut jouer ensemble.
+narrateur|Le doudou a un brin d'herbe, tout vert.
+narrateur|On est encore dans le jardin.
+narrateur|C'est encore le matin.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4804,7 +5042,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le matin. Il a joué dans le jardin. Aniss a fini sa phrase, près du doudou. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4944,7 +5182,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le matin.
+narrateur|Il a joué dans le jardin.
+narrateur|Aniss a fini sa phrase, près du doudou.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -4972,7 +5219,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans la cuisine. Un Le doudou est. Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, la chambre est un peu sombre. Le parquet craque, tout petit. Le doudou attend sur l'oreiller. On range les chaussons ? Oui. Le doudou va... Aniss s'arrête. Victorino pose les mains à plat. On laisse le temps. On attend la fin de la phrase. Le doudou va au lit. Bravo, Victorino. C'est du bon travail. Un rayon pose sur le plaid. Le plaid est encore frais, tout doux. On laisse le temps. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5108,9 +5355,23 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, Noé va dans la cuisine. Un
-enfant-m|Le doudou est.
-narrateur|Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>narrateur|Plus tard, la chambre est un peu sombre.
+narrateur|Le parquet craque, tout petit.
+narrateur|Le doudou attend sur l'oreiller.
+maman|On range les chaussons ?
+enfant-m|Oui.
+copain|Le doudou va...
+narrateur|Aniss s'arrête.
+narrateur|Victorino pose les mains à plat.
+papa|On laisse le temps.
+papa|On attend la fin de la phrase.
+copain|Le doudou va au lit.
+maman|Bravo, Victorino.
+maman|C'est du bon travail.
+narrateur|Un rayon pose sur le plaid.
+narrateur|Le plaid est encore frais, tout doux.
+maman|On laisse le temps.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5138,7 +5399,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois objets attendent, tout proches. Le ballon rouge, le seau bleu, ou le doudou ? On laisse le temps.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5302,7 +5563,9 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois objets attendent, tout proches.
+papa|Le ballon rouge, le seau bleu, ou le doudou ?
+maman|On laisse le temps.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5330,7 +5593,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le ballon rouge. la chambre est rangé. le matin est fini. Une pomme brille un peu. Noé range la tasse. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le ballon rouge. Le caoutchouc est un peu rêche. Le ballon est... Aniss cherche. Victorino attend. On laisse le temps. Le ballon est rouge. Bravo. Tu as attendu la fin. Il est rouge, oui. On peut jouer ensemble. Le ballon tapote le parquet, tout doux. On est encore dans la chambre. C'est encore le matin. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5466,7 +5729,24 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le ballon rouge. la chambre est rangé. le matin est fini. Une pomme brille un peu. Noé range la tasse. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le ballon rouge.
+narrateur|Le caoutchouc est un peu rêche.
+copain|Le ballon est...
+narrateur|Aniss cherche.
+narrateur|Victorino attend.
+papa|On laisse le temps.
+copain|Le ballon est rouge.
+maman|Bravo.
+maman|Tu as attendu la fin.
+enfant-m|Il est rouge, oui.
+papa|On peut jouer ensemble.
+narrateur|Le ballon tapote le parquet, tout doux.
+narrateur|On est encore dans la chambre.
+narrateur|C'est encore le matin.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5494,7 +5774,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le matin. Il a joué dans la chambre. Aniss a fini sa phrase, près du ballon rouge. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5634,7 +5914,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le matin.
+narrateur|Il a joué dans la chambre.
+narrateur|Aniss a fini sa phrase, près du ballon rouge.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5662,7 +5951,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de le seau bleu. Noé pose la chambre. le matin est derrière. Un ruban reste dans la poche. Noé dit merci à maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino pose le seau bleu. Le plastique sonne, tout creux. Le seau est... Aniss s'arrête. Victorino attend la fin. On laisse le temps. Le seau est bleu. Bravo, Victorino. Tu as su attendre. Il est bleu. On peut jouer ensemble. Le seau bleu est près des chaussons. On est encore dans la chambre. C'est encore le matin. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5798,7 +6087,24 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de le seau bleu. Noé pose la chambre. le matin est derrière. Un ruban reste dans la poche. Noé dit merci à maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino pose le seau bleu.
+narrateur|Le plastique sonne, tout creux.
+copain|Le seau est...
+narrateur|Aniss s'arrête.
+narrateur|Victorino attend la fin.
+maman|On laisse le temps.
+copain|Le seau est bleu.
+papa|Bravo, Victorino.
+papa|Tu as su attendre.
+enfant-m|Il est bleu.
+maman|On peut jouer ensemble.
+narrateur|Le seau bleu est près des chaussons.
+narrateur|On est encore dans la chambre.
+narrateur|C'est encore le matin.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5826,7 +6132,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le matin. Il a joué dans la chambre. Aniss a fini sa phrase, près du seau bleu. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -5966,7 +6272,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le matin.
+narrateur|Il a joué dans la chambre.
+narrateur|Aniss a fini sa phrase, près du seau bleu.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -5994,7 +6309,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Noé montre le doudou. Maman a vu le matin. Et la chambre. Il y a des miettes sur la table. Noé raccroche un linge. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le doudou. Le tissu est doux, un peu lourd. Le doudou va... Aniss cherche le mot. Victorino attend. On attend la fin de la phrase. Le doudou va venir. Bravo. Tu as laissé le temps. Il vient. On peut jouer ensemble. Le doudou retrouve l'oreiller frais. On est encore dans la chambre. C'est encore le matin. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6130,7 +6445,24 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Noé montre le doudou. Maman a vu le matin. Et la chambre. Il y a des miettes sur la table. Noé raccroche un linge. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le doudou.
+narrateur|Le tissu est doux, un peu lourd.
+copain|Le doudou va...
+narrateur|Aniss cherche le mot.
+narrateur|Victorino attend.
+papa|On attend la fin de la phrase.
+copain|Le doudou va venir.
+maman|Bravo.
+maman|Tu as laissé le temps.
+enfant-m|Il vient.
+papa|On peut jouer ensemble.
+narrateur|Le doudou retrouve l'oreiller frais.
+narrateur|On est encore dans la chambre.
+narrateur|C'est encore le matin.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6158,7 +6490,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le matin. Il a joué dans la chambre. Aniss a fini sa phrase, près du doudou. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6298,7 +6630,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le matin.
+narrateur|Il a joué dans la chambre.
+narrateur|Aniss a fini sa phrase, près du doudou.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6326,7 +6667,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Noé retrouve le parc. Un Le bac est. Il s'arrête. Noé laisse le temps. Il attend la fin de la phrase. Maman lui tient la main. On peut jouer ensemble.</t>
+          <t>Les joues d'Aniss sont encore chaudes. Une mèche colle à son front. Le parc est plus calme, tout doux. La sieste est finie ? Oui, maman. Le bac est... Aniss s'arrête. Victorino attend. On laisse le temps. On attend la fin de la phrase. Un oiseau saute près du seau. Le bac est chaud. Bravo. Tu as laissé le temps. On peut jouer ensemble. Le sable coule entre les doigts.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6466,9 +6807,22 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste. Noé retrouve le parc. Un
-enfant-m|Le bac est.
-narrateur|Il s'arrête. Noé laisse le temps. Il attend la fin de la phrase. Maman lui tient la main. On peut jouer ensemble.</t>
+          <t>narrateur|Les joues d'Aniss sont encore chaudes.
+narrateur|Une mèche colle à son front.
+narrateur|Le parc est plus calme, tout doux.
+maman|La sieste est finie ?
+enfant-m|Oui, maman.
+copain|Le bac est...
+narrateur|Aniss s'arrête.
+narrateur|Victorino attend.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+narrateur|Un oiseau saute près du seau.
+copain|Le bac est chaud.
+papa|Bravo.
+papa|Tu as laissé le temps.
+maman|On peut jouer ensemble.
+narrateur|Le sable coule entre les doigts.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -6500,7 +6854,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>On finit la phrase à sa place ?</t>
+          <t>Aniss n'a pas fini. On attend la fin ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6656,7 +7010,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|On finit la phrase à sa place ?</t>
+          <t>narrateur|Aniss n'a pas fini.
+maman|On attend la fin ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6684,7 +7039,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On laisse le temps. Noé retient le geste. Maman sourit. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Oui. On laisse le temps. On attend la fin de la phrase. Victorino garde les lèvres fermées. J'ai attendu. Bravo. Tu as laissé le temps. Une feuille tourne dans la flaque.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6824,7 +7179,14 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On laisse le temps. Noé retient le geste. Maman sourit. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>papa|Oui.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+narrateur|Victorino garde les lèvres fermées.
+enfant-m|J'ai attendu.
+maman|Bravo.
+maman|Tu as laissé le temps.
+narrateur|Une feuille tourne dans la flaque.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6852,7 +7214,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Trois coins de la maison attendent. La cuisine, le jardin, ou la chambre ? On attend la fin de la phrase.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7016,7 +7378,9 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Trois coins de la maison attendent.
+maman|La cuisine, le jardin, ou la chambre ?
+papa|On attend la fin de la phrase.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7044,7 +7408,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans le jardin. Un Le ballon a. Noé laisse le temps. Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, la cuisine sent le pain. La nappe est un peu rêche. Une miette dort près du sel. On se lave les mains ? Oui, maman. Le pain est... Aniss s'arrête. Victorino attend. On laisse le temps. On attend la fin de la phrase. Le pain est tiède. Bravo, Victorino. Tu as su attendre. L'eau coule, tout petit bruit. Le bol de cacao est encore tiède. On laisse le temps. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7180,10 +7544,23 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, Noé va dans le jardin. Un
-enfant-m|Le ballon a.
-narrateur|Noé laisse le temps.
-maman|Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>narrateur|Plus tard, la cuisine sent le pain.
+narrateur|La nappe est un peu rêche.
+narrateur|Une miette dort près du sel.
+maman|On se lave les mains ?
+enfant-m|Oui, maman.
+copain|Le pain est...
+narrateur|Aniss s'arrête.
+narrateur|Victorino attend.
+papa|On laisse le temps.
+papa|On attend la fin de la phrase.
+copain|Le pain est tiède.
+maman|Bravo, Victorino.
+maman|Tu as su attendre.
+narrateur|L'eau coule, tout petit bruit.
+narrateur|Le bol de cacao est encore tiède.
+maman|On laisse le temps.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7211,7 +7588,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois objets attendent, tout proches. Le ballon rouge, le seau bleu, ou le doudou ? On laisse le temps.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7375,7 +7752,9 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois objets attendent, tout proches.
+papa|Le ballon rouge, le seau bleu, ou le doudou ?
+maman|On laisse le temps.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7403,7 +7782,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi après la sieste. Puis la cuisine. Puis le ballon rouge. Un ballon s'immobilise. Noé range encore un peu, près de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le ballon rouge. Le caoutchouc est un peu rêche. Le ballon est... Aniss cherche. Victorino attend. On laisse le temps. Le ballon est rouge. Bravo. Tu as attendu la fin. Il est rouge, oui. On peut jouer ensemble. Le ballon s'immobilise près du bol. On est encore dans la cuisine. C'est encore après la sieste. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7539,7 +7918,24 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi après la sieste. Puis la cuisine. Puis le ballon rouge. Un ballon s'immobilise. Noé range encore un peu, près de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le ballon rouge.
+narrateur|Le caoutchouc est un peu rêche.
+copain|Le ballon est...
+narrateur|Aniss cherche.
+narrateur|Victorino attend.
+papa|On laisse le temps.
+copain|Le ballon est rouge.
+maman|Bravo.
+maman|Tu as attendu la fin.
+enfant-m|Il est rouge, oui.
+papa|On peut jouer ensemble.
+narrateur|Le ballon s'immobilise près du bol.
+narrateur|On est encore dans la cuisine.
+narrateur|C'est encore après la sieste.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7567,7 +7963,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu après la sieste. Il a joué dans la cuisine. Aniss a fini sa phrase, près du ballon rouge. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7707,7 +8103,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu après la sieste.
+narrateur|Il a joué dans la cuisine.
+narrateur|Aniss a fini sa phrase, près du ballon rouge.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7735,7 +8140,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Noé s'arrête près de le seau bleu. la cuisine est rangé. Un linge sèche à l'air. Noé range après la sieste dans sa tête, comme un souvenir. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino pose le seau bleu. Le plastique sonne, tout creux. Le seau est... Aniss s'arrête. Victorino attend la fin. On laisse le temps. Le seau est bleu. Bravo, Victorino. Tu as su attendre. Il est bleu. On peut jouer ensemble. Le seau fait un bruit, tout petit. On est encore dans la cuisine. C'est encore après la sieste. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7871,7 +8276,24 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Noé s'arrête près de le seau bleu. la cuisine est rangé. Un linge sèche à l'air. Noé range après la sieste dans sa tête, comme un souvenir. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino pose le seau bleu.
+narrateur|Le plastique sonne, tout creux.
+copain|Le seau est...
+narrateur|Aniss s'arrête.
+narrateur|Victorino attend la fin.
+maman|On laisse le temps.
+copain|Le seau est bleu.
+papa|Bravo, Victorino.
+papa|Tu as su attendre.
+enfant-m|Il est bleu.
+maman|On peut jouer ensemble.
+narrateur|Le seau fait un bruit, tout petit.
+narrateur|On est encore dans la cuisine.
+narrateur|C'est encore après la sieste.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7899,7 +8321,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu après la sieste. Il a joué dans la cuisine. Aniss a fini sa phrase, près du seau bleu. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8039,7 +8461,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu après la sieste.
+narrateur|Il a joué dans la cuisine.
+narrateur|Aniss a fini sa phrase, près du seau bleu.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8067,7 +8498,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Noé se souvient de après la sieste. Et de la cuisine. Et de le doudou. Une feuille tombe. Noé écoute maman encore une fois. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le doudou. Le tissu est doux, un peu lourd. Le doudou va... Aniss cherche le mot. Victorino attend. On attend la fin de la phrase. Le doudou va venir. Bravo. Tu as laissé le temps. Il vient. On peut jouer ensemble. Le doudou est tiède, comme les joues. On est encore dans la cuisine. C'est encore après la sieste. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8203,7 +8634,24 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Noé se souvient de après la sieste. Et de la cuisine. Et de le doudou. Une feuille tombe. Noé écoute maman encore une fois. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le doudou.
+narrateur|Le tissu est doux, un peu lourd.
+copain|Le doudou va...
+narrateur|Aniss cherche le mot.
+narrateur|Victorino attend.
+papa|On attend la fin de la phrase.
+copain|Le doudou va venir.
+maman|Bravo.
+maman|Tu as laissé le temps.
+enfant-m|Il vient.
+papa|On peut jouer ensemble.
+narrateur|Le doudou est tiède, comme les joues.
+narrateur|On est encore dans la cuisine.
+narrateur|C'est encore après la sieste.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8231,7 +8679,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu après la sieste. Il a joué dans la cuisine. Aniss a fini sa phrase, près du doudou. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8371,7 +8819,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu après la sieste.
+narrateur|Il a joué dans la cuisine.
+narrateur|Aniss a fini sa phrase, près du doudou.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8399,7 +8856,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans le jardin. Un Le seau a. Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, le jardin a de l'herbe mouillée. Une feuille colle à la chaussette. Le banc de bois reste froid. Tu sens l'herbe ? Elle sent vert. Le ballon a... Aniss cherche. Victorino attend la fin. On laisse le temps. On attend la fin de la phrase. Le ballon a de l'herbe. Bravo. Tu as laissé le temps. Une goutte glisse sur le ballon. L'ombre de l'arbre est ronde, tout calme. On laisse le temps. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8535,9 +8992,23 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, Noé va dans le jardin. Un
-enfant-m|Le seau a.
-narrateur|Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>narrateur|Plus tard, le jardin a de l'herbe mouillée.
+narrateur|Une feuille colle à la chaussette.
+narrateur|Le banc de bois reste froid.
+papa|Tu sens l'herbe ?
+enfant-m|Elle sent vert.
+copain|Le ballon a...
+narrateur|Aniss cherche.
+narrateur|Victorino attend la fin.
+maman|On laisse le temps.
+maman|On attend la fin de la phrase.
+copain|Le ballon a de l'herbe.
+papa|Bravo.
+papa|Tu as laissé le temps.
+narrateur|Une goutte glisse sur le ballon.
+narrateur|L'ombre de l'arbre est ronde, tout calme.
+maman|On laisse le temps.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8565,7 +9036,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois objets attendent, tout proches. Le ballon rouge, le seau bleu, ou le doudou ? On laisse le temps.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8729,7 +9200,9 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois objets attendent, tout proches.
+papa|Le ballon rouge, le seau bleu, ou le doudou ?
+maman|On laisse le temps.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8757,7 +9230,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec le ballon rouge. Après le jardin. Près de après la sieste. Noé s'arrête. Un chat miaule une fois. Noé tend le ballon rouge à papa. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le ballon rouge. Le caoutchouc est un peu rêche. Le ballon est... Aniss cherche. Victorino attend. On laisse le temps. Le ballon est rouge. Bravo. Tu as attendu la fin. Il est rouge, oui. On peut jouer ensemble. Le ballon sèche au soleil, tout lent. On est encore dans le jardin. C'est encore après la sieste. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8893,7 +9366,24 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de après la sieste. Noé s'arrête. Un chat miaule une fois. Noé tend le ballon rouge à papa. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le ballon rouge.
+narrateur|Le caoutchouc est un peu rêche.
+copain|Le ballon est...
+narrateur|Aniss cherche.
+narrateur|Victorino attend.
+papa|On laisse le temps.
+copain|Le ballon est rouge.
+maman|Bravo.
+maman|Tu as attendu la fin.
+enfant-m|Il est rouge, oui.
+papa|On peut jouer ensemble.
+narrateur|Le ballon sèche au soleil, tout lent.
+narrateur|On est encore dans le jardin.
+narrateur|C'est encore après la sieste.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -8921,7 +9411,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu après la sieste. Il a joué dans le jardin. Aniss a fini sa phrase, près du ballon rouge. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9061,7 +9551,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu après la sieste.
+narrateur|Il a joué dans le jardin.
+narrateur|Aniss a fini sa phrase, près du ballon rouge.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9089,7 +9588,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Noé range le jardin. le seau bleu reste près de après la sieste. On souffle doucement. Noé plie un pull. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino pose le seau bleu. Le plastique sonne, tout creux. Le seau est... Aniss s'arrête. Victorino attend la fin. On laisse le temps. Le seau est bleu. Bravo, Victorino. Tu as su attendre. Il est bleu. On peut jouer ensemble. Le seau a une ombre ronde, tout calme. On est encore dans le jardin. C'est encore après la sieste. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9225,7 +9724,24 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Noé range le jardin. le seau bleu reste près de après la sieste. On souffle doucement. Noé plie un pull. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino pose le seau bleu.
+narrateur|Le plastique sonne, tout creux.
+copain|Le seau est...
+narrateur|Aniss s'arrête.
+narrateur|Victorino attend la fin.
+maman|On laisse le temps.
+copain|Le seau est bleu.
+papa|Bravo, Victorino.
+papa|Tu as su attendre.
+enfant-m|Il est bleu.
+maman|On peut jouer ensemble.
+narrateur|Le seau a une ombre ronde, tout calme.
+narrateur|On est encore dans le jardin.
+narrateur|C'est encore après la sieste.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9253,7 +9769,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu après la sieste. Il a joué dans le jardin. Aniss a fini sa phrase, près du seau bleu. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9393,7 +9909,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu après la sieste.
+narrateur|Il a joué dans le jardin.
+narrateur|Aniss a fini sa phrase, près du seau bleu.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9421,7 +9946,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Un panier est posé sur le banc. Noé répète tout bas le geste. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le doudou. Le tissu est doux, un peu lourd. Le doudou va... Aniss cherche le mot. Victorino attend. On attend la fin de la phrase. Le doudou va venir. Bravo. Tu as laissé le temps. Il vient. On peut jouer ensemble. Le doudou s'assoit sur le banc froid. On est encore dans le jardin. C'est encore après la sieste. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9557,7 +10082,24 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Un panier est posé sur le banc. Noé répète tout bas le geste. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le doudou.
+narrateur|Le tissu est doux, un peu lourd.
+copain|Le doudou va...
+narrateur|Aniss cherche le mot.
+narrateur|Victorino attend.
+papa|On attend la fin de la phrase.
+copain|Le doudou va venir.
+maman|Bravo.
+maman|Tu as laissé le temps.
+enfant-m|Il vient.
+papa|On peut jouer ensemble.
+narrateur|Le doudou s'assoit sur le banc froid.
+narrateur|On est encore dans le jardin.
+narrateur|C'est encore après la sieste.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9585,7 +10127,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu après la sieste. Il a joué dans le jardin. Aniss a fini sa phrase, près du doudou. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9725,7 +10267,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu après la sieste.
+narrateur|Il a joué dans le jardin.
+narrateur|Aniss a fini sa phrase, près du doudou.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9753,7 +10304,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans le jardin. Un Le doudou a. Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, la chambre est un peu sombre. Le parquet craque, tout petit. Le doudou attend sur l'oreiller. On range les chaussons ? Oui. Le doudou va... Aniss s'arrête. Victorino pose les mains à plat. On laisse le temps. On attend la fin de la phrase. Le doudou va au lit. Bravo, Victorino. C'est du bon travail. Un rayon pose sur le plaid. L'oreiller a encore un pli chaud. On laisse le temps. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9889,9 +10440,23 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, Noé va dans le jardin. Un
-enfant-m|Le doudou a.
-narrateur|Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>narrateur|Plus tard, la chambre est un peu sombre.
+narrateur|Le parquet craque, tout petit.
+narrateur|Le doudou attend sur l'oreiller.
+maman|On range les chaussons ?
+enfant-m|Oui.
+copain|Le doudou va...
+narrateur|Aniss s'arrête.
+narrateur|Victorino pose les mains à plat.
+papa|On laisse le temps.
+papa|On attend la fin de la phrase.
+copain|Le doudou va au lit.
+maman|Bravo, Victorino.
+maman|C'est du bon travail.
+narrateur|Un rayon pose sur le plaid.
+narrateur|L'oreiller a encore un pli chaud.
+maman|On laisse le temps.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -9919,7 +10484,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois objets attendent, tout proches. Le ballon rouge, le seau bleu, ou le doudou ? On laisse le temps.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10083,7 +10648,9 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois objets attendent, tout proches.
+papa|Le ballon rouge, le seau bleu, ou le doudou ?
+maman|On laisse le temps.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10111,7 +10678,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le ballon rouge. la chambre est rangé. après la sieste est fini. La lumière est claire. Papa n'est pas loin. Noé les rejoint. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le ballon rouge. Le caoutchouc est un peu rêche. Le ballon est... Aniss cherche. Victorino attend. On laisse le temps. Le ballon est rouge. Bravo. Tu as attendu la fin. Il est rouge, oui. On peut jouer ensemble. Le ballon reste au pied du lit. On est encore dans la chambre. C'est encore après la sieste. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10247,7 +10814,24 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le ballon rouge. la chambre est rangé. après la sieste est fini. La lumière est claire. Papa n'est pas loin. Noé les rejoint. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le ballon rouge.
+narrateur|Le caoutchouc est un peu rêche.
+copain|Le ballon est...
+narrateur|Aniss cherche.
+narrateur|Victorino attend.
+papa|On laisse le temps.
+copain|Le ballon est rouge.
+maman|Bravo.
+maman|Tu as attendu la fin.
+enfant-m|Il est rouge, oui.
+papa|On peut jouer ensemble.
+narrateur|Le ballon reste au pied du lit.
+narrateur|On est encore dans la chambre.
+narrateur|C'est encore après la sieste.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10275,7 +10859,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu après la sieste. Il a joué dans la chambre. Aniss a fini sa phrase, près du ballon rouge. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10415,7 +10999,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu après la sieste.
+narrateur|Il a joué dans la chambre.
+narrateur|Aniss a fini sa phrase, près du ballon rouge.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10443,7 +11036,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de le seau bleu. Noé pose la chambre. après la sieste est derrière. On se tient la main. Noé prend la main de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino pose le seau bleu. Le plastique sonne, tout creux. Le seau est... Aniss s'arrête. Victorino attend la fin. On laisse le temps. Le seau est bleu. Bravo, Victorino. Tu as su attendre. Il est bleu. On peut jouer ensemble. Le seau bleu veille près du plaid. On est encore dans la chambre. C'est encore après la sieste. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10583,7 +11176,24 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de le seau bleu. Noé pose la chambre. après la sieste est derrière. On se tient la main. Noé prend la main de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino pose le seau bleu.
+narrateur|Le plastique sonne, tout creux.
+copain|Le seau est...
+narrateur|Aniss s'arrête.
+narrateur|Victorino attend la fin.
+maman|On laisse le temps.
+copain|Le seau est bleu.
+papa|Bravo, Victorino.
+papa|Tu as su attendre.
+enfant-m|Il est bleu.
+maman|On peut jouer ensemble.
+narrateur|Le seau bleu veille près du plaid.
+narrateur|On est encore dans la chambre.
+narrateur|C'est encore après la sieste.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10611,7 +11221,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu après la sieste. Il a joué dans la chambre. Aniss a fini sa phrase, près du seau bleu. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10751,7 +11361,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu après la sieste.
+narrateur|Il a joué dans la chambre.
+narrateur|Aniss a fini sa phrase, près du seau bleu.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10779,7 +11398,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Noé montre le doudou. Maman a vu après la sieste. Et la chambre. On écoute jusqu'au bout. Noé pose sa tête un moment. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le doudou. Le tissu est doux, un peu lourd. Le doudou va... Aniss cherche le mot. Victorino attend. On attend la fin de la phrase. Le doudou va venir. Bravo. Tu as laissé le temps. Il vient. On peut jouer ensemble. Le doudou glisse sous la couverture. On est encore dans la chambre. C'est encore après la sieste. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10915,7 +11534,24 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Noé montre le doudou. Maman a vu après la sieste. Et la chambre. On écoute jusqu'au bout. Noé pose sa tête un moment. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le doudou.
+narrateur|Le tissu est doux, un peu lourd.
+copain|Le doudou va...
+narrateur|Aniss cherche le mot.
+narrateur|Victorino attend.
+papa|On attend la fin de la phrase.
+copain|Le doudou va venir.
+maman|Bravo.
+maman|Tu as laissé le temps.
+enfant-m|Il vient.
+papa|On peut jouer ensemble.
+narrateur|Le doudou glisse sous la couverture.
+narrateur|On est encore dans la chambre.
+narrateur|C'est encore après la sieste.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -10943,7 +11579,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu après la sieste. Il a joué dans la chambre. Aniss a fini sa phrase, près du doudou. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11083,7 +11719,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu après la sieste.
+narrateur|Il a joué dans la chambre.
+narrateur|Aniss a fini sa phrase, près du doudou.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11111,7 +11756,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Le parc devient calme. Un Je rentre avec. Il cherche le mot. Noé laisse le temps. Il attend la fin de la phrase. Papa sourit. On peut jouer ensemble.</t>
+          <t>Le parc devient bleu, tout doux. Le banc a perdu sa chaleur. Un lampadaire s'allume, tout loin. On rentre bientôt. Encore un peu. Je rentre avec... Aniss cherche le mot. Victorino attend la fin. On laisse le temps. On attend la fin de la phrase. Je rentre avec vous. Bravo, Victorino. Tu as su attendre. On peut jouer ensemble. Le seau bleu penche sur le sable.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11247,9 +11892,21 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir. Le parc devient calme. Un
-enfant-m|Je rentre avec. Il cherche le mot.
-narrateur|Noé laisse le temps. Il attend la fin de la phrase. Papa sourit. On peut jouer ensemble.</t>
+          <t>narrateur|Le parc devient bleu, tout doux.
+narrateur|Le banc a perdu sa chaleur.
+narrateur|Un lampadaire s'allume, tout loin.
+papa|On rentre bientôt.
+enfant-m|Encore un peu.
+copain|Je rentre avec...
+narrateur|Aniss cherche le mot.
+narrateur|Victorino attend la fin.
+maman|On laisse le temps.
+maman|On attend la fin de la phrase.
+copain|Je rentre avec vous.
+papa|Bravo, Victorino.
+papa|Tu as su attendre.
+maman|On peut jouer ensemble.
+narrateur|Le seau bleu penche sur le sable.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -11281,7 +11938,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>On attend la fin de la phrase ?</t>
+          <t>Aniss parle tout doucement. On attend la fin de la phrase ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11437,7 +12094,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|On attend la fin de la phrase ?</t>
+          <t>narrateur|Aniss parle tout doucement.
+papa|On attend la fin de la phrase ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11465,7 +12123,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On laisse le temps. Noé hoche la tête. On continue, avec maman. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Oui. On laisse le temps. On attend la fin de la phrase. Victorino hoche la tête. Jusqu'au bout. Bravo. On peut jouer ensemble. Le lampadaire fait un rond jaune.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11605,7 +12263,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On laisse le temps. Noé hoche la tête. On continue, avec maman. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>maman|Oui.
+maman|On laisse le temps.
+papa|On attend la fin de la phrase.
+narrateur|Victorino hoche la tête.
+enfant-m|Jusqu'au bout.
+papa|Bravo.
+papa|On peut jouer ensemble.
+narrateur|Le lampadaire fait un rond jaune.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11633,7 +12298,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Trois coins de la maison attendent. La cuisine, le jardin, ou la chambre ? On attend la fin de la phrase.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11797,7 +12462,9 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Trois coins de la maison attendent.
+maman|La cuisine, le jardin, ou la chambre ?
+papa|On attend la fin de la phrase.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11825,7 +12492,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans la chambre. Un Le ballon va. Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, la cuisine sent le pain. La nappe est un peu rêche. Une miette dort près du sel. On se lave les mains ? Oui, maman. Le pain est... Aniss s'arrête. Victorino attend. On laisse le temps. On attend la fin de la phrase. Le pain est tiède. Bravo, Victorino. Tu as su attendre. L'eau coule, tout petit bruit. La lampe allonge l'ombre du pain. On laisse le temps. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11961,9 +12628,23 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, Noé va dans la chambre. Un
-enfant-m|Le ballon va.
-narrateur|Noé laisse le temps. Maman reste tout près. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>narrateur|Plus tard, la cuisine sent le pain.
+narrateur|La nappe est un peu rêche.
+narrateur|Une miette dort près du sel.
+maman|On se lave les mains ?
+enfant-m|Oui, maman.
+copain|Le pain est...
+narrateur|Aniss s'arrête.
+narrateur|Victorino attend.
+papa|On laisse le temps.
+papa|On attend la fin de la phrase.
+copain|Le pain est tiède.
+maman|Bravo, Victorino.
+maman|Tu as su attendre.
+narrateur|L'eau coule, tout petit bruit.
+narrateur|La lampe allonge l'ombre du pain.
+maman|On laisse le temps.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -11991,7 +12672,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois objets attendent, tout proches. Le ballon rouge, le seau bleu, ou le doudou ? On laisse le temps.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12155,7 +12836,9 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois objets attendent, tout proches.
+papa|Le ballon rouge, le seau bleu, ou le doudou ?
+maman|On laisse le temps.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12183,7 +12866,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le soir. Puis la cuisine. Puis le ballon rouge. Une chaussette est encore sablée. Noé essuie ses mains. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le ballon rouge. Le caoutchouc est un peu rêche. Le ballon est... Aniss cherche. Victorino attend. On laisse le temps. Le ballon est rouge. Bravo. Tu as attendu la fin. Il est rouge, oui. On peut jouer ensemble. L'ombre du ballon danse sur la nappe. On est encore dans la cuisine. C'est encore le soir. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12323,7 +13006,24 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le soir. Puis la cuisine. Puis le ballon rouge. Une chaussette est encore sablée. Noé essuie ses mains. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le ballon rouge.
+narrateur|Le caoutchouc est un peu rêche.
+copain|Le ballon est...
+narrateur|Aniss cherche.
+narrateur|Victorino attend.
+papa|On laisse le temps.
+copain|Le ballon est rouge.
+maman|Bravo.
+maman|Tu as attendu la fin.
+enfant-m|Il est rouge, oui.
+papa|On peut jouer ensemble.
+narrateur|L'ombre du ballon danse sur la nappe.
+narrateur|On est encore dans la cuisine.
+narrateur|C'est encore le soir.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12351,7 +13051,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le soir. Il a joué dans la cuisine. Aniss a fini sa phrase, près du ballon rouge. La veilleuse reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12491,7 +13191,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le soir.
+narrateur|Il a joué dans la cuisine.
+narrateur|Aniss a fini sa phrase, près du ballon rouge.
+narrateur|La veilleuse reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12519,7 +13228,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Noé s'arrête près de le seau bleu. la cuisine est rangé. On dit merci. Noé sourit. Maman sourit aussi. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino pose le seau bleu. Le plastique sonne, tout creux. Le seau est... Aniss s'arrête. Victorino attend la fin. On laisse le temps. Le seau est bleu. Bravo, Victorino. Tu as su attendre. Il est bleu. On peut jouer ensemble. Le seau reflète la lampe, tout rond. On est encore dans la cuisine. C'est encore le soir. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12655,7 +13364,24 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Noé s'arrête près de le seau bleu. la cuisine est rangé. On dit merci. Noé sourit. Maman sourit aussi. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino pose le seau bleu.
+narrateur|Le plastique sonne, tout creux.
+copain|Le seau est...
+narrateur|Aniss s'arrête.
+narrateur|Victorino attend la fin.
+maman|On laisse le temps.
+copain|Le seau est bleu.
+papa|Bravo, Victorino.
+papa|Tu as su attendre.
+enfant-m|Il est bleu.
+maman|On peut jouer ensemble.
+narrateur|Le seau reflète la lampe, tout rond.
+narrateur|On est encore dans la cuisine.
+narrateur|C'est encore le soir.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12683,7 +13409,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le soir. Il a joué dans la cuisine. Aniss a fini sa phrase, près du seau bleu. La veilleuse reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12823,7 +13549,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le soir.
+narrateur|Il a joué dans la cuisine.
+narrateur|Aniss a fini sa phrase, près du seau bleu.
+narrateur|La veilleuse reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12851,7 +13586,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Noé se souvient de le soir. Et de la cuisine. Et de le doudou. Le savon sent bon. Noé serre la main de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le doudou. Le tissu est doux, un peu lourd. Le doudou va... Aniss cherche le mot. Victorino attend. On attend la fin de la phrase. Le doudou va venir. Bravo. Tu as laissé le temps. Il vient. On peut jouer ensemble. Le doudou a une miette sur l'oreille. On est encore dans la cuisine. C'est encore le soir. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -12991,7 +13726,24 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Noé se souvient de le soir. Et de la cuisine. Et de le doudou. Le savon sent bon. Noé serre la main de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le doudou.
+narrateur|Le tissu est doux, un peu lourd.
+copain|Le doudou va...
+narrateur|Aniss cherche le mot.
+narrateur|Victorino attend.
+papa|On attend la fin de la phrase.
+copain|Le doudou va venir.
+maman|Bravo.
+maman|Tu as laissé le temps.
+enfant-m|Il vient.
+papa|On peut jouer ensemble.
+narrateur|Le doudou a une miette sur l'oreille.
+narrateur|On est encore dans la cuisine.
+narrateur|C'est encore le soir.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13019,7 +13771,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le soir. Il a joué dans la cuisine. Aniss a fini sa phrase, près du doudou. La veilleuse reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13159,7 +13911,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le soir.
+narrateur|Il a joué dans la cuisine.
+narrateur|Aniss a fini sa phrase, près du doudou.
+narrateur|La veilleuse reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13187,7 +13948,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans la chambre. Un Le seau va. Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, le jardin a de l'herbe mouillée. Une feuille colle à la chaussette. Le banc de bois reste froid. Tu sens l'herbe ? Elle sent vert. Le ballon a... Aniss cherche. Victorino attend la fin. On laisse le temps. On attend la fin de la phrase. Le ballon a de l'herbe. Bravo. Tu as laissé le temps. Une goutte glisse sur le ballon. Le jardin sent la terre, tout frais. On laisse le temps. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13323,9 +14084,23 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, Noé va dans la chambre. Un
-enfant-m|Le seau va.
-narrateur|Noé laisse le temps. Maman montre le geste, lentement. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>narrateur|Plus tard, le jardin a de l'herbe mouillée.
+narrateur|Une feuille colle à la chaussette.
+narrateur|Le banc de bois reste froid.
+papa|Tu sens l'herbe ?
+enfant-m|Elle sent vert.
+copain|Le ballon a...
+narrateur|Aniss cherche.
+narrateur|Victorino attend la fin.
+maman|On laisse le temps.
+maman|On attend la fin de la phrase.
+copain|Le ballon a de l'herbe.
+papa|Bravo.
+papa|Tu as laissé le temps.
+narrateur|Une goutte glisse sur le ballon.
+narrateur|Le jardin sent la terre, tout frais.
+maman|On laisse le temps.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13353,7 +14128,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois objets attendent, tout proches. Le ballon rouge, le seau bleu, ou le doudou ? On laisse le temps.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13517,7 +14292,9 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois objets attendent, tout proches.
+papa|Le ballon rouge, le seau bleu, ou le doudou ?
+maman|On laisse le temps.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13545,7 +14322,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec le ballon rouge. Après le jardin. Près de le soir. Noé s'arrête. On rit un peu. Noé marche près de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le ballon rouge. Le caoutchouc est un peu rêche. Le ballon est... Aniss cherche. Victorino attend. On laisse le temps. Le ballon est rouge. Bravo. Tu as attendu la fin. Il est rouge, oui. On peut jouer ensemble. Le ballon roule vers la haie sombre. On est encore dans le jardin. C'est encore le soir. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13681,7 +14458,24 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le soir. Noé s'arrête. On rit un peu. Noé marche près de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le ballon rouge.
+narrateur|Le caoutchouc est un peu rêche.
+copain|Le ballon est...
+narrateur|Aniss cherche.
+narrateur|Victorino attend.
+papa|On laisse le temps.
+copain|Le ballon est rouge.
+maman|Bravo.
+maman|Tu as attendu la fin.
+enfant-m|Il est rouge, oui.
+papa|On peut jouer ensemble.
+narrateur|Le ballon roule vers la haie sombre.
+narrateur|On est encore dans le jardin.
+narrateur|C'est encore le soir.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13709,7 +14503,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le soir. Il a joué dans le jardin. Aniss a fini sa phrase, près du ballon rouge. La veilleuse reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13849,7 +14643,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le soir.
+narrateur|Il a joué dans le jardin.
+narrateur|Aniss a fini sa phrase, près du ballon rouge.
+narrateur|La veilleuse reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13877,7 +14680,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Noé range le jardin. le seau bleu reste près de le soir. Un vélo passe au loin. Noé pose le jardin à sa place. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino pose le seau bleu. Le plastique sonne, tout creux. Le seau est... Aniss s'arrête. Victorino attend la fin. On laisse le temps. Le seau est bleu. Bravo, Victorino. Tu as su attendre. Il est bleu. On peut jouer ensemble. Le seau bleu penche près du portail. On est encore dans le jardin. C'est encore le soir. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14013,7 +14816,24 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Noé range le jardin. le seau bleu reste près de le soir. Un vélo passe au loin. Noé pose le jardin à sa place. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino pose le seau bleu.
+narrateur|Le plastique sonne, tout creux.
+copain|Le seau est...
+narrateur|Aniss s'arrête.
+narrateur|Victorino attend la fin.
+maman|On laisse le temps.
+copain|Le seau est bleu.
+papa|Bravo, Victorino.
+papa|Tu as su attendre.
+enfant-m|Il est bleu.
+maman|On peut jouer ensemble.
+narrateur|Le seau bleu penche près du portail.
+narrateur|On est encore dans le jardin.
+narrateur|C'est encore le soir.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14041,7 +14861,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le soir. Il a joué dans le jardin. Aniss a fini sa phrase, près du seau bleu. La veilleuse reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14181,7 +15001,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le soir.
+narrateur|Il a joué dans le jardin.
+narrateur|Aniss a fini sa phrase, près du seau bleu.
+narrateur|La veilleuse reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14209,7 +15038,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le doudou est là. le jardin aussi. le soir reste dans le souvenir. Un crochet tient bien le manteau. Noé ferme le sac. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le doudou. Le tissu est doux, un peu lourd. Le doudou va... Aniss cherche le mot. Victorino attend. On attend la fin de la phrase. Le doudou va venir. Bravo. Tu as laissé le temps. Il vient. On peut jouer ensemble. Le doudou sent la terre, un peu. On est encore dans le jardin. C'est encore le soir. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14345,7 +15174,24 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Le doudou est là. le jardin aussi. le soir reste dans le souvenir. Un crochet tient bien le manteau. Noé ferme le sac. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le doudou.
+narrateur|Le tissu est doux, un peu lourd.
+copain|Le doudou va...
+narrateur|Aniss cherche le mot.
+narrateur|Victorino attend.
+papa|On attend la fin de la phrase.
+copain|Le doudou va venir.
+maman|Bravo.
+maman|Tu as laissé le temps.
+enfant-m|Il vient.
+papa|On peut jouer ensemble.
+narrateur|Le doudou sent la terre, un peu.
+narrateur|On est encore dans le jardin.
+narrateur|C'est encore le soir.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14373,7 +15219,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le soir. Il a joué dans le jardin. Aniss a fini sa phrase, près du doudou. La veilleuse reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14513,7 +15359,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le soir.
+narrateur|Il a joué dans le jardin.
+narrateur|Aniss a fini sa phrase, près du doudou.
+narrateur|La veilleuse reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14541,7 +15396,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Noé va dans la chambre. Un Le doudou va. Noé laisse le temps. Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>Plus tard, la chambre est un peu sombre. Le parquet craque, tout petit. Le doudou attend sur l'oreiller. On range les chaussons ? Oui. Le doudou va... Aniss s'arrête. Victorino pose les mains à plat. On laisse le temps. On attend la fin de la phrase. Le doudou va au lit. Bravo, Victorino. C'est du bon travail. Un rayon pose sur le plaid. La veilleuse fait un rond orange. On laisse le temps. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14677,10 +15532,23 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Plus tard, Noé va dans la chambre. Un
-enfant-m|Le doudou va.
-narrateur|Noé laisse le temps.
-maman|Je suis là. On laisse le temps. On attend la fin de la phrase. On peut jouer ensemble.</t>
+          <t>narrateur|Plus tard, la chambre est un peu sombre.
+narrateur|Le parquet craque, tout petit.
+narrateur|Le doudou attend sur l'oreiller.
+maman|On range les chaussons ?
+enfant-m|Oui.
+copain|Le doudou va...
+narrateur|Aniss s'arrête.
+narrateur|Victorino pose les mains à plat.
+papa|On laisse le temps.
+papa|On attend la fin de la phrase.
+copain|Le doudou va au lit.
+maman|Bravo, Victorino.
+maman|C'est du bon travail.
+narrateur|Un rayon pose sur le plaid.
+narrateur|La veilleuse fait un rond orange.
+maman|On laisse le temps.
+papa|On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14708,7 +15576,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois objets attendent, tout proches. Le ballon rouge, le seau bleu, ou le doudou ? On laisse le temps.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14872,7 +15740,9 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois objets attendent, tout proches.
+papa|Le ballon rouge, le seau bleu, ou le doudou ?
+maman|On laisse le temps.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -14900,7 +15770,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le ballon rouge. la chambre est rangé. le soir est fini. Le vent est doux. Noé enfile ses chaussons. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le ballon rouge. Le caoutchouc est un peu rêche. Le ballon est... Aniss cherche. Victorino attend. On laisse le temps. Le ballon est rouge. Bravo. Tu as attendu la fin. Il est rouge, oui. On peut jouer ensemble. Le ballon dort sous la veilleuse. On est encore dans la chambre. C'est encore le soir. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15036,7 +15906,24 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le ballon rouge. la chambre est rangé. le soir est fini. Le vent est doux. Noé enfile ses chaussons. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le ballon rouge.
+narrateur|Le caoutchouc est un peu rêche.
+copain|Le ballon est...
+narrateur|Aniss cherche.
+narrateur|Victorino attend.
+papa|On laisse le temps.
+copain|Le ballon est rouge.
+maman|Bravo.
+maman|Tu as attendu la fin.
+enfant-m|Il est rouge, oui.
+papa|On peut jouer ensemble.
+narrateur|Le ballon dort sous la veilleuse.
+narrateur|On est encore dans la chambre.
+narrateur|C'est encore le soir.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15064,7 +15951,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le soir. Il a joué dans la chambre. Aniss a fini sa phrase, près du ballon rouge. La veilleuse reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15204,7 +16091,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le soir.
+narrateur|Il a joué dans la chambre.
+narrateur|Aniss a fini sa phrase, près du ballon rouge.
+narrateur|La veilleuse reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15232,7 +16128,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de le seau bleu. Noé pose la chambre. le soir est derrière. L'eau coule, tout petit bruit. Noé s'assoit près de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino pose le seau bleu. Le plastique sonne, tout creux. Le seau est... Aniss s'arrête. Victorino attend la fin. On laisse le temps. Le seau est bleu. Bravo, Victorino. Tu as su attendre. Il est bleu. On peut jouer ensemble. Le seau bleu est rangé, tout sage. On est encore dans la chambre. C'est encore le soir. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15368,7 +16264,24 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de le seau bleu. Noé pose la chambre. le soir est derrière. L'eau coule, tout petit bruit. Noé s'assoit près de maman. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino pose le seau bleu.
+narrateur|Le plastique sonne, tout creux.
+copain|Le seau est...
+narrateur|Aniss s'arrête.
+narrateur|Victorino attend la fin.
+maman|On laisse le temps.
+copain|Le seau est bleu.
+papa|Bravo, Victorino.
+papa|Tu as su attendre.
+enfant-m|Il est bleu.
+maman|On peut jouer ensemble.
+narrateur|Le seau bleu est rangé, tout sage.
+narrateur|On est encore dans la chambre.
+narrateur|C'est encore le soir.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15396,7 +16309,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le soir. Il a joué dans la chambre. Aniss a fini sa phrase, près du seau bleu. La veilleuse reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15536,7 +16449,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le soir.
+narrateur|Il a joué dans la chambre.
+narrateur|Aniss a fini sa phrase, près du seau bleu.
+narrateur|La veilleuse reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15564,7 +16486,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Noé montre le doudou. Maman a vu le soir. Et la chambre. Une cloche tinte, tout loin. Noé ferme la porte, tout doux. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>Victorino prend le doudou. Le tissu est doux, un peu lourd. Le doudou va... Aniss cherche le mot. Victorino attend. On attend la fin de la phrase. Le doudou va venir. Bravo. Tu as laissé le temps. Il vient. On peut jouer ensemble. Le doudou retrouve l'oreiller, tout chaud. On est encore dans la chambre. C'est encore le soir. On laisse le temps. On attend la fin de la phrase. J'ai attendu. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15700,7 +16622,24 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Noé montre le doudou. Maman a vu le soir. Et la chambre. Une cloche tinte, tout loin. Noé ferme la porte, tout doux. On laisse le temps. On attend la fin de la phrase. On laisse le temps. Noé dit merci à maman.</t>
+          <t>narrateur|Victorino prend le doudou.
+narrateur|Le tissu est doux, un peu lourd.
+copain|Le doudou va...
+narrateur|Aniss cherche le mot.
+narrateur|Victorino attend.
+papa|On attend la fin de la phrase.
+copain|Le doudou va venir.
+maman|Bravo.
+maman|Tu as laissé le temps.
+enfant-m|Il vient.
+papa|On peut jouer ensemble.
+narrateur|Le doudou retrouve l'oreiller, tout chaud.
+narrateur|On est encore dans la chambre.
+narrateur|C'est encore le soir.
+papa|On laisse le temps.
+maman|On attend la fin de la phrase.
+enfant-m|J'ai attendu.
+papa|Bravo, Victorino.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15728,7 +16667,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Merci, maman. Merci, papa. Bravo, Victorino. Tu as fait du bon travail. Tu as laissé le temps. Victorino a vécu le soir. Il a joué dans la chambre. Aniss a fini sa phrase, près du doudou. La veilleuse reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15868,7 +16807,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+papa|Tu as laissé le temps.
+narrateur|Victorino a vécu le soir.
+narrateur|Il a joué dans la chambre.
+narrateur|Aniss a fini sa phrase, près du doudou.
+narrateur|La veilleuse reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -15890,7 +16838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15928,6 +16876,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-005.xlsx
+++ b/stories/arbres/TREE-DIF-005.xlsx
@@ -1197,12 +1197,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Au bout du village, le parc s'ouvre. Un platane jette une ombre ronde. Des moineaux picorent près du bac. Le toboggan en métal brille un peu. Du sable fin colle déjà sur la rampe. Ça sent le soleil et la poussière. Tu vois le toboggan, Aniss ? Oui, papa. Il brille. Le banc est encore un peu froid. En ce moment, Aniss tire sa chaussure. Je veux glisser ! Nino est déjà près de l'échelle. Ses lèvres bougent, tout lentement. Je veux le. On l'écoute, Aniss ? Oui.</t>
+          <t>Au bout du village, le parc s'ouvre. Un platane jette une ombre ronde. Des moineaux picorent près du bac. Le toboggan en métal brille un peu. Du sable fin colle déjà sur la rampe. Ça sent le soleil et la poussière. Tu vois le toboggan, Aniss ? Oui, papa. Il brille. Le banc est encore un peu froid. En ce moment, Aniss tire sa chaussure. Je veux glisser ! Nino est déjà près de l'échelle. Ses lèvres bougent, tout lentement. Je veux le. Nino te parle, Aniss ? Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Au bout du village, le parc s'ouvre. Un platane jette une ombre ronde. Des moineaux picorent près du bac. Le toboggan en métal brille un peu. Du sable fin colle déjà sur la rampe. Ça sent le soleil et la poussière. Tu vois le toboggan, Aniss ? Oui, papa. Il brille. Le banc est encore un peu froid. En ce moment, Aniss tire sa chaussure. Je veux glisser ! Nino est déjà près de l'échelle. Ses lèvres bougent, tout lentement. Je veux le. On l'écoute, Aniss ? Oui.</t>
+          <t>Au bout du village, le parc s'ouvre. Un platane jette une ombre ronde. Des moineaux picorent près du bac. Le toboggan en métal brille un peu. Du sable fin colle déjà sur la rampe. Ça sent le soleil et la poussière. Tu vois le toboggan, Aniss ? Oui, papa. Il brille. Le banc est encore un peu froid. En ce moment, Aniss tire sa chaussure. Je veux glisser ! Nino est déjà près de l'échelle. Ses lèvres bougent, tout lentement. Je veux le. Nino te parle, Aniss ? Oui.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
 narrateur|Nino est déjà près de l'échelle.
 narrateur|Ses lèvres bougent, tout lentement.
 copain|Je veux le.
-papa|On l'écoute, Aniss ?
+papa|Nino te parle, Aniss ?
 enfant-m|Oui.</t>
         </is>
       </c>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nino reprend, tout doux. Le toboggan a du sable. J'ai attendu. Merci, Aniss. On peut avancer, maintenant. L'ombre du platane est longue. Où va-t-on d'abord ?</t>
+          <t>Nino reprend, tout doux. Le toboggan a du sable. On y va. Merci, Aniss. On peut avancer, maintenant. L'ombre du platane est longue. Où va-t-on d'abord ?</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Nino reprend, tout doux. Le toboggan a du sable. J'ai attendu. Merci, Aniss. On peut avancer, maintenant. L'ombre du platane est longue. Où va-t-on d'abord ?</t>
+          <t>Nino reprend, tout doux. Le toboggan a du sable. On y va. Merci, Aniss. On peut avancer, maintenant. L'ombre du platane est longue. Où va-t-on d'abord ?</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
         <is>
           <t>narrateur|Nino reprend, tout doux.
 copain|Le toboggan a du sable.
-enfant-m|J'ai attendu.
+enfant-m|On y va.
 papa|Merci, Aniss.
 maman|On peut avancer, maintenant.
 narrateur|L'ombre du platane est longue.
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Du sable froid remplit le bac. Un rond rouge dépasse, à peine. Le ballon est. Aniss creuse, tout doux, et attend. Il est sous le sable ? Le ballon est sous le sable. Je le sors. Le rouge sort, un peu sablé. Les doigts d'Aniss sont un peu rouges. Vous l'avez, tous les deux. Maintenant, le toboggan ! Ils portent le ballon vers l'échelle.</t>
+          <t>Du sable froid remplit le bac. Un rond rouge dépasse, à peine. Le ballon est. Aniss creuse, tout doux, et attend. Il est sous le sable ? Le ballon est sous le sable. Je le sors. Le rouge sort, un peu sablé. Les doigts d'Aniss sont un peu rouges. Vous l'avez, tous les deux. Ils grimpent, le ballon contre la hanche. Puis ça file, tout court, tout vif.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Du sable froid remplit le bac. Un rond rouge dépasse, à peine. Le ballon est. Aniss creuse, tout doux, et attend. Il est sous le sable ? Le ballon est sous le sable. Je le sors. Le rouge sort, un peu sablé. Les doigts d'Aniss sont un peu rouges. Vous l'avez, tous les deux. Maintenant, le toboggan ! Ils portent le ballon vers l'échelle.</t>
+          <t>Du sable froid remplit le bac. Un rond rouge dépasse, à peine. Le ballon est. Aniss creuse, tout doux, et attend. Il est sous le sable ? Le ballon est sous le sable. Je le sors. Le rouge sort, un peu sablé. Les doigts d'Aniss sont un peu rouges. Vous l'avez, tous les deux. Ils grimpent, le ballon contre la hanche. Puis ça file, tout court, tout vif.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2826,8 +2826,8 @@
 narrateur|Le rouge sort, un peu sablé.
 narrateur|Les doigts d'Aniss sont un peu rouges.
 maman|Vous l'avez, tous les deux.
-enfant-m|Maintenant, le toboggan !
-narrateur|Ils portent le ballon vers l'échelle.</t>
+narrateur|Ils grimpent, le ballon contre la hanche.
+narrateur|Puis ça file, tout court, tout vif.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>La rosée brille encore sur l'herbe. Le seau bleu attend près du bac. Le seau est. Aniss tient l'anse, sans tirer. Il va le dire. Le seau est lourd. On verse, alors. Ils raclent le sable de la rampe. Le bleu se remplit, grain après grain. Sous les doigts, le métal pique un peu. La rampe redevient lisse. On peut glisser !</t>
+          <t>La rosée brille encore sur l'herbe. Le seau bleu attend près du bac. Le seau est. Aniss tient l'anse, sans tirer. Il va le dire. Le seau est lourd. On verse, alors. Ils raclent le sable de la rampe. Le bleu se remplit, grain après grain. Sous les doigts, le métal pique un peu. La rampe redevient lisse. Ça file, tout d'un coup.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>La rosée brille encore sur l'herbe. Le seau bleu attend près du bac. Le seau est. Aniss tient l'anse, sans tirer. Il va le dire. Le seau est lourd. On verse, alors. Ils raclent le sable de la rampe. Le bleu se remplit, grain après grain. Sous les doigts, le métal pique un peu. La rampe redevient lisse. On peut glisser !</t>
+          <t>La rosée brille encore sur l'herbe. Le seau bleu attend près du bac. Le seau est. Aniss tient l'anse, sans tirer. Il va le dire. Le seau est lourd. On verse, alors. Ils raclent le sable de la rampe. Le bleu se remplit, grain après grain. Sous les doigts, le métal pique un peu. La rampe redevient lisse. Ça file, tout d'un coup.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
 narrateur|Le bleu se remplit, grain après grain.
 narrateur|Sous les doigts, le métal pique un peu.
 papa|La rampe redevient lisse.
-enfant-m|On peut glisser !</t>
+narrateur|Ça file, tout d'un coup.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>L'ombre du platane est longue. Le doudou dort dans le bac, tout sablé. Le doudou est. Aniss garde les mains, et attend. Il le veut, ce doudou ? Le doudou est tout sablé. On le tapote. Le sable tombe, un nuage minuscule. Nino le serre contre sa joue. Un moineau crie, tout près. Il est prêt, maintenant. On grimpe, avec lui.</t>
+          <t>L'ombre du platane est longue. Le doudou dort dans le bac, tout sablé. Le doudou est. Aniss garde les mains, et attend. Il le veut, ce doudou ? Le doudou est tout sablé. On le tapote. Le sable tombe, un nuage minuscule. Nino le serre contre sa joue. Un moineau crie, tout près. Il est prêt, maintenant. Ils glissent, le doudou entre eux.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>L'ombre du platane est longue. Le doudou dort dans le bac, tout sablé. Le doudou est. Aniss garde les mains, et attend. Il le veut, ce doudou ? Le doudou est tout sablé. On le tapote. Le sable tombe, un nuage minuscule. Nino le serre contre sa joue. Un moineau crie, tout près. Il est prêt, maintenant. On grimpe, avec lui.</t>
+          <t>L'ombre du platane est longue. Le doudou dort dans le bac, tout sablé. Le doudou est. Aniss garde les mains, et attend. Il le veut, ce doudou ? Le doudou est tout sablé. On le tapote. Le sable tombe, un nuage minuscule. Nino le serre contre sa joue. Un moineau crie, tout près. Il est prêt, maintenant. Ils glissent, le doudou entre eux.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
 narrateur|Nino le serre contre sa joue.
 narrateur|Un moineau crie, tout près.
 maman|Il est prêt, maintenant.
-enfant-m|On grimpe, avec lui.</t>
+narrateur|Ils glissent, le doudou entre eux.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sous les doigts, le métal pique un peu. Le ballon rouge coince un barreau. Le ballon va. Aniss ouvre les mains, en bas, et attend. Tu le laisses dire ? Le ballon va tomber. Je suis là. Nino pousse, tout doux. Le rouge atterrit dans les mains d'Aniss. Un moineau crie, tout près. Le chemin est libre. On monte, puis on glisse !</t>
+          <t>Sous les doigts, le métal pique un peu. Le ballon rouge coince un barreau. Le ballon va. Aniss ouvre les mains, en bas, et attend. Tu le laisses dire ? Le ballon va tomber. Je suis là. Nino pousse, tout doux. Le rouge atterrit dans les mains d'Aniss. Un moineau crie, tout près. Le chemin est libre. Ils montent, puis ça dévale.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Sous les doigts, le métal pique un peu. Le ballon rouge coince un barreau. Le ballon va. Aniss ouvre les mains, en bas, et attend. Tu le laisses dire ? Le ballon va tomber. Je suis là. Nino pousse, tout doux. Le rouge atterrit dans les mains d'Aniss. Un moineau crie, tout près. Le chemin est libre. On monte, puis on glisse !</t>
+          <t>Sous les doigts, le métal pique un peu. Le ballon rouge coince un barreau. Le ballon va. Aniss ouvre les mains, en bas, et attend. Tu le laisses dire ? Le ballon va tomber. Je suis là. Nino pousse, tout doux. Le rouge atterrit dans les mains d'Aniss. Un moineau crie, tout près. Le chemin est libre. Ils montent, puis ça dévale.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4275,7 +4275,7 @@
 narrateur|Le rouge atterrit dans les mains d'Aniss.
 narrateur|Un moineau crie, tout près.
 papa|Le chemin est libre.
-enfant-m|On monte, puis on glisse !</t>
+narrateur|Ils montent, puis ça dévale.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>L'ombre du platane est longue. Le seau bleu pend près du haut. Le seau va. Aniss reste un barreau plus bas. On l'écoute, d'accord ? Le seau va nous aider. Je te le tends. Nino pousse le sable, tout lentement. Les grains tombent dans le bleu. Du sable froid remplit le bac. La rampe redevient glissante. À nous !</t>
+          <t>L'ombre du platane est longue. Le seau bleu pend près du haut. Le seau va. Aniss reste un barreau plus bas. On l'écoute, d'accord ? Le seau va nous aider. Je te le tends. Nino pousse le sable, tout lentement. Les grains tombent dans le bleu. Du sable froid remplit le bac. La rampe redevient glissante. Ils dévalent, le seau à la main.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>L'ombre du platane est longue. Le seau bleu pend près du haut. Le seau va. Aniss reste un barreau plus bas. On l'écoute, d'accord ? Le seau va nous aider. Je te le tends. Nino pousse le sable, tout lentement. Les grains tombent dans le bleu. Du sable froid remplit le bac. La rampe redevient glissante. À nous !</t>
+          <t>L'ombre du platane est longue. Le seau bleu pend près du haut. Le seau va. Aniss reste un barreau plus bas. On l'écoute, d'accord ? Le seau va nous aider. Je te le tends. Nino pousse le sable, tout lentement. Les grains tombent dans le bleu. Du sable froid remplit le bac. La rampe redevient glissante. Ils dévalent, le seau à la main.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
 narrateur|Les grains tombent dans le bleu.
 narrateur|Du sable froid remplit le bac.
 maman|La rampe redevient glissante.
-enfant-m|À nous !</t>
+narrateur|Ils dévalent, le seau à la main.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>La rosée brille encore sur l'herbe. Le doudou est coincé sur un barreau. Le doudou va. Aniss ne le prend pas, et attend. Sa phrase n'est pas finie. Le doudou va avec moi. Je te le passe. Nino le glisse sous son bras. Ils montent, barreau après barreau. Sous les doigts, le métal pique un peu. Vous y êtes, tout en haut. On glisse ensemble !</t>
+          <t>La rosée brille encore sur l'herbe. Le doudou est coincé sur un barreau. Le doudou va. Aniss ne le prend pas, et attend. Il cherche encore. Le doudou va avec moi. Je te le passe. Nino le glisse sous son bras. Ils montent, barreau après barreau. Sous les doigts, le métal pique un peu. Vous y êtes, tout en haut. Ils glissent, le doudou au milieu.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>La rosée brille encore sur l'herbe. Le doudou est coincé sur un barreau. Le doudou va. Aniss ne le prend pas, et attend. Sa phrase n'est pas finie. Le doudou va avec moi. Je te le passe. Nino le glisse sous son bras. Ils montent, barreau après barreau. Sous les doigts, le métal pique un peu. Vous y êtes, tout en haut. On glisse ensemble !</t>
+          <t>La rosée brille encore sur l'herbe. Le doudou est coincé sur un barreau. Le doudou va. Aniss ne le prend pas, et attend. Il cherche encore. Le doudou va avec moi. Je te le passe. Nino le glisse sous son bras. Ils montent, barreau après barreau. Sous les doigts, le métal pique un peu. Vous y êtes, tout en haut. Ils glissent, le doudou au milieu.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4986,14 +4986,14 @@
 narrateur|Le doudou est coincé sur un barreau.
 copain|Le doudou va.
 narrateur|Aniss ne le prend pas, et attend.
-maman|Sa phrase n'est pas finie.
+maman|Il cherche encore.
 copain|Le doudou va avec moi.
 enfant-m|Je te le passe.
 narrateur|Nino le glisse sous son bras.
 narrateur|Ils montent, barreau après barreau.
 narrateur|Sous les doigts, le métal pique un peu.
 papa|Vous y êtes, tout en haut.
-enfant-m|On glisse ensemble !</t>
+narrateur|Ils glissent, le doudou au milieu.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>La lumière pèse, toute blanche. Au toucher, le toboggan est tiède. Sous les paumes, le sable brûle un peu. Je veux glisser, vite ! Nino parle, tout bas, tout lent. Le bac est. Aniss se tait, les mains au barreau. Tu l'entends, ce murmure ? Oui, maman. C'est Nino. Le parc dore, après la sieste. Une cigale frotte, tout loin. J'attends sa phrase.</t>
+          <t>La lumière pèse, toute blanche. Au toucher, le toboggan est tiède. Sous les paumes, le sable brûle un peu. Je veux glisser, vite ! Nino parle, tout bas, tout lent. Le bac est. Aniss se tait, les mains au barreau. Tu l'entends, ce murmure ? Oui, maman. C'est Nino. Le parc dore, après la sieste. Une cigale frotte, tout loin. J'attends.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>La lumière pèse, toute blanche. Au toucher, le toboggan est tiède. Sous les paumes, le sable brûle un peu. Je veux glisser, vite ! Nino parle, tout bas, tout lent. Le bac est. Aniss se tait, les mains au barreau. Tu l'entends, ce murmure ? Oui, maman. C'est Nino. Le parc dore, après la sieste. Une cigale frotte, tout loin. J'attends sa phrase.</t>
+          <t>La lumière pèse, toute blanche. Au toucher, le toboggan est tiède. Sous les paumes, le sable brûle un peu. Je veux glisser, vite ! Nino parle, tout bas, tout lent. Le bac est. Aniss se tait, les mains au barreau. Tu l'entends, ce murmure ? Oui, maman. C'est Nino. Le parc dore, après la sieste. Une cigale frotte, tout loin. J'attends.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6805,7 +6805,7 @@
 enfant-m|C'est Nino.
 papa|Le parc dore, après la sieste.
 narrateur|Une cigale frotte, tout loin.
-enfant-m|J'attends sa phrase.</t>
+enfant-m|J'attends.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Nino reprend, tout doux. Le bac est plein. J'ai attendu. Merci, Aniss. On peut avancer, maintenant. La lumière pèse, toute blanche. Où va-t-on d'abord ?</t>
+          <t>Nino reprend, tout doux. Le bac est plein. On y va. Merci, Aniss. On peut avancer, maintenant. La lumière pèse, toute blanche. Où va-t-on d'abord ?</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Nino reprend, tout doux. Le bac est plein. J'ai attendu. Merci, Aniss. On peut avancer, maintenant. La lumière pèse, toute blanche. Où va-t-on d'abord ?</t>
+          <t>Nino reprend, tout doux. Le bac est plein. On y va. Merci, Aniss. On peut avancer, maintenant. La lumière pèse, toute blanche. Où va-t-on d'abord ?</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
         <is>
           <t>narrateur|Nino reprend, tout doux.
 copain|Le bac est plein.
-enfant-m|J'ai attendu.
+enfant-m|On y va.
 papa|Merci, Aniss.
 maman|On peut avancer, maintenant.
 narrateur|La lumière pèse, toute blanche.
@@ -7762,12 +7762,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sous les paumes, le sable brûle un peu. Un rond rouge dépasse, à peine. Le ballon est. Aniss creuse, tout doux, et attend. Il est sous le sable ? Le ballon est sous le sable. Je le sors. Le rouge sort, un peu sablé. Une goutte coule sur la tempe d'Aniss. Vous l'avez, tous les deux. Maintenant, le toboggan ! Ils portent le ballon vers l'échelle.</t>
+          <t>Sous les paumes, le sable brûle un peu. Un rond rouge dépasse, à peine. Le ballon est. Aniss creuse, tout doux, et attend. Il est sous le sable ? Le ballon est sous le sable. Je le sors. Le rouge sort, un peu sablé. Une goutte coule sur la tempe d'Aniss. Vous l'avez, tous les deux. Ils grimpent, le ballon contre la hanche. Puis ça file, tout court, tout vif.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Sous les paumes, le sable brûle un peu. Un rond rouge dépasse, à peine. Le ballon est. Aniss creuse, tout doux, et attend. Il est sous le sable ? Le ballon est sous le sable. Je le sors. Le rouge sort, un peu sablé. Une goutte coule sur la tempe d'Aniss. Vous l'avez, tous les deux. Maintenant, le toboggan ! Ils portent le ballon vers l'échelle.</t>
+          <t>Sous les paumes, le sable brûle un peu. Un rond rouge dépasse, à peine. Le ballon est. Aniss creuse, tout doux, et attend. Il est sous le sable ? Le ballon est sous le sable. Je le sors. Le rouge sort, un peu sablé. Une goutte coule sur la tempe d'Aniss. Vous l'avez, tous les deux. Ils grimpent, le ballon contre la hanche. Puis ça file, tout court, tout vif.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -7908,8 +7908,8 @@
 narrateur|Le rouge sort, un peu sablé.
 narrateur|Une goutte coule sur la tempe d'Aniss.
 maman|Vous l'avez, tous les deux.
-enfant-m|Maintenant, le toboggan !
-narrateur|Ils portent le ballon vers l'échelle.</t>
+narrateur|Ils grimpent, le ballon contre la hanche.
+narrateur|Puis ça file, tout court, tout vif.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>L'air sent la poussière chaude. Le seau bleu attend près du bac. Le seau est. Aniss tient l'anse, sans tirer. Il va le dire. Le seau est lourd. On verse, alors. Ils raclent le sable de la rampe. Le bleu se remplit, grain après grain. Au toucher, le toboggan est tiède. La rampe redevient lisse. On peut glisser !</t>
+          <t>L'air sent la poussière chaude. Le seau bleu attend près du bac. Le seau est. Aniss tient l'anse, sans tirer. Il va le dire. Le seau est lourd. On verse, alors. Ils raclent le sable de la rampe. Le bleu se remplit, grain après grain. Au toucher, le toboggan est tiède. La rampe redevient lisse. Ça file, tout d'un coup.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>L'air sent la poussière chaude. Le seau bleu attend près du bac. Le seau est. Aniss tient l'anse, sans tirer. Il va le dire. Le seau est lourd. On verse, alors. Ils raclent le sable de la rampe. Le bleu se remplit, grain après grain. Au toucher, le toboggan est tiède. La rampe redevient lisse. On peut glisser !</t>
+          <t>L'air sent la poussière chaude. Le seau bleu attend près du bac. Le seau est. Aniss tient l'anse, sans tirer. Il va le dire. Le seau est lourd. On verse, alors. Ils raclent le sable de la rampe. Le bleu se remplit, grain après grain. Au toucher, le toboggan est tiède. La rampe redevient lisse. Ça file, tout d'un coup.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
 narrateur|Le bleu se remplit, grain après grain.
 narrateur|Au toucher, le toboggan est tiède.
 papa|La rampe redevient lisse.
-enfant-m|On peut glisser !</t>
+narrateur|Ça file, tout d'un coup.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>La lumière pèse, toute blanche. Le doudou dort dans le bac, tout sablé. Le doudou est. Aniss garde les mains, et attend. Il le veut, ce doudou ? Le doudou est tout sablé. On le tapote. Le sable tombe, un nuage minuscule. Nino le serre contre sa joue. Une cigale frotte, tout loin. Il est prêt, maintenant. On grimpe, avec lui.</t>
+          <t>La lumière pèse, toute blanche. Le doudou dort dans le bac, tout sablé. Le doudou est. Aniss garde les mains, et attend. Il le veut, ce doudou ? Le doudou est tout sablé. On le tapote. Le sable tombe, un nuage minuscule. Nino le serre contre sa joue. Une cigale frotte, tout loin. Il est prêt, maintenant. Ils glissent, le doudou entre eux.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>La lumière pèse, toute blanche. Le doudou dort dans le bac, tout sablé. Le doudou est. Aniss garde les mains, et attend. Il le veut, ce doudou ? Le doudou est tout sablé. On le tapote. Le sable tombe, un nuage minuscule. Nino le serre contre sa joue. Une cigale frotte, tout loin. Il est prêt, maintenant. On grimpe, avec lui.</t>
+          <t>La lumière pèse, toute blanche. Le doudou dort dans le bac, tout sablé. Le doudou est. Aniss garde les mains, et attend. Il le veut, ce doudou ? Le doudou est tout sablé. On le tapote. Le sable tombe, un nuage minuscule. Nino le serre contre sa joue. Une cigale frotte, tout loin. Il est prêt, maintenant. Ils glissent, le doudou entre eux.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -8627,7 +8627,7 @@
 narrateur|Nino le serre contre sa joue.
 narrateur|Une cigale frotte, tout loin.
 maman|Il est prêt, maintenant.
-enfant-m|On grimpe, avec lui.</t>
+narrateur|Ils glissent, le doudou entre eux.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Au toucher, le toboggan est tiède. Le ballon rouge coince un barreau. Le ballon va. Aniss ouvre les mains, en bas, et attend. Tu le laisses dire ? Le ballon va tomber. Je suis là. Nino pousse, tout doux. Le rouge atterrit dans les mains d'Aniss. Une cigale frotte, tout loin. Le chemin est libre. On monte, puis on glisse !</t>
+          <t>Au toucher, le toboggan est tiède. Le ballon rouge coince un barreau. Le ballon va. Aniss ouvre les mains, en bas, et attend. Tu le laisses dire ? Le ballon va tomber. Je suis là. Nino pousse, tout doux. Le rouge atterrit dans les mains d'Aniss. Une cigale frotte, tout loin. Le chemin est libre. Ils montent, puis ça dévale.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Au toucher, le toboggan est tiède. Le ballon rouge coince un barreau. Le ballon va. Aniss ouvre les mains, en bas, et attend. Tu le laisses dire ? Le ballon va tomber. Je suis là. Nino pousse, tout doux. Le rouge atterrit dans les mains d'Aniss. Une cigale frotte, tout loin. Le chemin est libre. On monte, puis on glisse !</t>
+          <t>Au toucher, le toboggan est tiède. Le ballon rouge coince un barreau. Le ballon va. Aniss ouvre les mains, en bas, et attend. Tu le laisses dire ? Le ballon va tomber. Je suis là. Nino pousse, tout doux. Le rouge atterrit dans les mains d'Aniss. Une cigale frotte, tout loin. Le chemin est libre. Ils montent, puis ça dévale.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -9357,7 +9357,7 @@
 narrateur|Le rouge atterrit dans les mains d'Aniss.
 narrateur|Une cigale frotte, tout loin.
 papa|Le chemin est libre.
-enfant-m|On monte, puis on glisse !</t>
+narrateur|Ils montent, puis ça dévale.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>La lumière pèse, toute blanche. Le seau bleu pend près du haut. Le seau va. Aniss reste un barreau plus bas. On l'écoute, d'accord ? Le seau va nous aider. Je te le tends. Nino pousse le sable, tout lentement. Les grains tombent dans le bleu. Sous les paumes, le sable brûle un peu. La rampe redevient glissante. À nous !</t>
+          <t>La lumière pèse, toute blanche. Le seau bleu pend près du haut. Le seau va. Aniss reste un barreau plus bas. On l'écoute, d'accord ? Le seau va nous aider. Je te le tends. Nino pousse le sable, tout lentement. Les grains tombent dans le bleu. Sous les paumes, le sable brûle un peu. La rampe redevient glissante. Ils dévalent, le seau à la main.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>La lumière pèse, toute blanche. Le seau bleu pend près du haut. Le seau va. Aniss reste un barreau plus bas. On l'écoute, d'accord ? Le seau va nous aider. Je te le tends. Nino pousse le sable, tout lentement. Les grains tombent dans le bleu. Sous les paumes, le sable brûle un peu. La rampe redevient glissante. À nous !</t>
+          <t>La lumière pèse, toute blanche. Le seau bleu pend près du haut. Le seau va. Aniss reste un barreau plus bas. On l'écoute, d'accord ? Le seau va nous aider. Je te le tends. Nino pousse le sable, tout lentement. Les grains tombent dans le bleu. Sous les paumes, le sable brûle un peu. La rampe redevient glissante. Ils dévalent, le seau à la main.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -9716,7 +9716,7 @@
 narrateur|Les grains tombent dans le bleu.
 narrateur|Sous les paumes, le sable brûle un peu.
 maman|La rampe redevient glissante.
-enfant-m|À nous !</t>
+narrateur|Ils dévalent, le seau à la main.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>L'air sent la poussière chaude. Le doudou est coincé sur un barreau. Le doudou va. Aniss ne le prend pas, et attend. Sa phrase n'est pas finie. Le doudou va avec moi. Je te le passe. Nino le glisse sous son bras. Ils montent, barreau après barreau. Au toucher, le toboggan est tiède. Vous y êtes, tout en haut. On glisse ensemble !</t>
+          <t>L'air sent la poussière chaude. Le doudou est coincé sur un barreau. Le doudou va. Aniss ne le prend pas, et attend. Il cherche encore. Le doudou va avec moi. Je te le passe. Nino le glisse sous son bras. Ils montent, barreau après barreau. Au toucher, le toboggan est tiède. Vous y êtes, tout en haut. Ils glissent, le doudou au milieu.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>L'air sent la poussière chaude. Le doudou est coincé sur un barreau. Le doudou va. Aniss ne le prend pas, et attend. Sa phrase n'est pas finie. Le doudou va avec moi. Je te le passe. Nino le glisse sous son bras. Ils montent, barreau après barreau. Au toucher, le toboggan est tiède. Vous y êtes, tout en haut. On glisse ensemble !</t>
+          <t>L'air sent la poussière chaude. Le doudou est coincé sur un barreau. Le doudou va. Aniss ne le prend pas, et attend. Il cherche encore. Le doudou va avec moi. Je te le passe. Nino le glisse sous son bras. Ils montent, barreau après barreau. Au toucher, le toboggan est tiède. Vous y êtes, tout en haut. Ils glissent, le doudou au milieu.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -10068,14 +10068,14 @@
 narrateur|Le doudou est coincé sur un barreau.
 copain|Le doudou va.
 narrateur|Aniss ne le prend pas, et attend.
-maman|Sa phrase n'est pas finie.
+maman|Il cherche encore.
 copain|Le doudou va avec moi.
 enfant-m|Je te le passe.
 narrateur|Nino le glisse sous son bras.
 narrateur|Ils montent, barreau après barreau.
 narrateur|Au toucher, le toboggan est tiède.
 papa|Vous y êtes, tout en haut.
-enfant-m|On glisse ensemble !</t>
+narrateur|Ils glissent, le doudou au milieu.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>La lumière devient orange, tout doux. Un lampadaire fait un petit tic. Le sable colle sur le toboggan. Je veux glisser avant la nuit ! Nino cherche encore un mot. Je rentre avec. Aniss attend, tout calme. Le métal refroidit, ce soir. Tu vois le sable, Aniss ? Oui. Sur le toboggan. L'ombre violette touche déjà l'herbe. On glisse après sa phrase.</t>
+          <t>La lumière devient orange, tout doux. Un lampadaire fait un petit tic. Le sable colle sur le toboggan. Je veux glisser avant la nuit ! Nino cherche encore un mot. Je glisse avec. Aniss attend, tout calme. Le métal refroidit, ce soir. Tu vois le sable, Aniss ? Oui. Sur le toboggan. L'ombre violette touche déjà l'herbe. On glisse après.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>La lumière devient orange, tout doux. Un lampadaire fait un petit tic. Le sable colle sur le toboggan. Je veux glisser avant la nuit ! Nino cherche encore un mot. Je rentre avec. Aniss attend, tout calme. Le métal refroidit, ce soir. Tu vois le sable, Aniss ? Oui. Sur le toboggan. L'ombre violette touche déjà l'herbe. On glisse après sa phrase.</t>
+          <t>La lumière devient orange, tout doux. Un lampadaire fait un petit tic. Le sable colle sur le toboggan. Je veux glisser avant la nuit ! Nino cherche encore un mot. Je glisse avec. Aniss attend, tout calme. Le métal refroidit, ce soir. Tu vois le sable, Aniss ? Oui. Sur le toboggan. L'ombre violette touche déjà l'herbe. On glisse après.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -11880,14 +11880,14 @@
 narrateur|Le sable colle sur le toboggan.
 enfant-m|Je veux glisser avant la nuit !
 narrateur|Nino cherche encore un mot.
-copain|Je rentre avec.
+copain|Je glisse avec.
 narrateur|Aniss attend, tout calme.
 papa|Le métal refroidit, ce soir.
 maman|Tu vois le sable, Aniss ?
 enfant-m|Oui.
 enfant-m|Sur le toboggan.
 narrateur|L'ombre violette touche déjà l'herbe.
-enfant-m|On glisse après sa phrase.</t>
+enfant-m|On glisse après.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Nino reprend, tout doux. Je rentre avec toi. J'ai attendu. Merci, Aniss. On peut avancer, maintenant. L'ombre violette touche déjà l'herbe. Où va-t-on d'abord ?</t>
+          <t>Nino reprend, tout doux. Je glisse avec toi. On y va. Merci, Aniss. On peut avancer, maintenant. L'ombre violette touche déjà l'herbe. Où va-t-on d'abord ?</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Nino reprend, tout doux. Je rentre avec toi. J'ai attendu. Merci, Aniss. On peut avancer, maintenant. L'ombre violette touche déjà l'herbe. Où va-t-on d'abord ?</t>
+          <t>Nino reprend, tout doux. Je glisse avec toi. On y va. Merci, Aniss. On peut avancer, maintenant. L'ombre violette touche déjà l'herbe. Où va-t-on d'abord ?</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -12243,8 +12243,8 @@
       <c r="AW62" t="inlineStr">
         <is>
           <t>narrateur|Nino reprend, tout doux.
-copain|Je rentre avec toi.
-enfant-m|J'ai attendu.
+copain|Je glisse avec toi.
+enfant-m|On y va.
 papa|Merci, Aniss.
 maman|On peut avancer, maintenant.
 narrateur|L'ombre violette touche déjà l'herbe.
@@ -12844,12 +12844,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Voilà le sable, déjà refroidi, tout fin. Un rond rouge dépasse, à peine. Le ballon est. Aniss creuse, tout doux, et attend. Il est sous le sable ? Le ballon est sous le sable. Je le sors. Le rouge sort, un peu sablé. Les genoux d'Aniss ont du sable froid. Vous l'avez, tous les deux. Maintenant, le toboggan ! Ils portent le ballon vers l'échelle.</t>
+          <t>Voilà le sable, déjà refroidi, tout fin. Un rond rouge dépasse, à peine. Le ballon est. Aniss creuse, tout doux, et attend. Il est sous le sable ? Le ballon est sous le sable. Je le sors. Le rouge sort, un peu sablé. Les genoux d'Aniss ont du sable froid. Vous l'avez, tous les deux. Ils grimpent, le ballon contre la hanche. Puis ça file, tout court, tout vif.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Voilà le sable, déjà refroidi, tout fin. Un rond rouge dépasse, à peine. Le ballon est. Aniss creuse, tout doux, et attend. Il est sous le sable ? Le ballon est sous le sable. Je le sors. Le rouge sort, un peu sablé. Les genoux d'Aniss ont du sable froid. Vous l'avez, tous les deux. Maintenant, le toboggan ! Ils portent le ballon vers l'échelle.</t>
+          <t>Voilà le sable, déjà refroidi, tout fin. Un rond rouge dépasse, à peine. Le ballon est. Aniss creuse, tout doux, et attend. Il est sous le sable ? Le ballon est sous le sable. Je le sors. Le rouge sort, un peu sablé. Les genoux d'Aniss ont du sable froid. Vous l'avez, tous les deux. Ils grimpent, le ballon contre la hanche. Puis ça file, tout court, tout vif.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -12994,8 +12994,8 @@
 narrateur|Le rouge sort, un peu sablé.
 narrateur|Les genoux d'Aniss ont du sable froid.
 maman|Vous l'avez, tous les deux.
-enfant-m|Maintenant, le toboggan !
-narrateur|Ils portent le ballon vers l'échelle.</t>
+narrateur|Ils grimpent, le ballon contre la hanche.
+narrateur|Puis ça file, tout court, tout vif.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
@@ -13207,12 +13207,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>La lumière devient orange, tout doux. Le seau bleu attend près du bac. Le seau est. Aniss tient l'anse, sans tirer. Il va le dire. Le seau est lourd. On verse, alors. Ils raclent le sable de la rampe. Le bleu se remplit, grain après grain. Maintenant le toboggan refroidit. La rampe redevient lisse. On peut glisser !</t>
+          <t>La lumière devient orange, tout doux. Le seau bleu attend près du bac. Le seau est. Aniss tient l'anse, sans tirer. Il va le dire. Le seau est lourd. On verse, alors. Ils raclent le sable de la rampe. Le bleu se remplit, grain après grain. Maintenant le toboggan refroidit. La rampe redevient lisse. Ça file, tout d'un coup.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>La lumière devient orange, tout doux. Le seau bleu attend près du bac. Le seau est. Aniss tient l'anse, sans tirer. Il va le dire. Le seau est lourd. On verse, alors. Ils raclent le sable de la rampe. Le bleu se remplit, grain après grain. Maintenant le toboggan refroidit. La rampe redevient lisse. On peut glisser !</t>
+          <t>La lumière devient orange, tout doux. Le seau bleu attend près du bac. Le seau est. Aniss tient l'anse, sans tirer. Il va le dire. Le seau est lourd. On verse, alors. Ils raclent le sable de la rampe. Le bleu se remplit, grain après grain. Maintenant le toboggan refroidit. La rampe redevient lisse. Ça file, tout d'un coup.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13354,7 +13354,7 @@
 narrateur|Le bleu se remplit, grain après grain.
 narrateur|Maintenant le toboggan refroidit.
 papa|La rampe redevient lisse.
-enfant-m|On peut glisser !</t>
+narrateur|Ça file, tout d'un coup.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -13566,12 +13566,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>L'ombre violette touche déjà l'herbe. Le doudou dort dans le bac, tout sablé. Le doudou est. Aniss garde les mains, et attend. Il le veut, ce doudou ? Le doudou est tout sablé. On le tapote. Le sable tombe, un nuage minuscule. Nino le serre contre sa joue. Un lampadaire fait un petit tic. Il est prêt, maintenant. On grimpe, avec lui.</t>
+          <t>L'ombre violette touche déjà l'herbe. Le doudou dort dans le bac, tout sablé. Le doudou est. Aniss garde les mains, et attend. Il le veut, ce doudou ? Le doudou est tout sablé. On le tapote. Le sable tombe, un nuage minuscule. Nino le serre contre sa joue. Un lampadaire fait un petit tic. Il est prêt, maintenant. Ils glissent, le doudou entre eux.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>L'ombre violette touche déjà l'herbe. Le doudou dort dans le bac, tout sablé. Le doudou est. Aniss garde les mains, et attend. Il le veut, ce doudou ? Le doudou est tout sablé. On le tapote. Le sable tombe, un nuage minuscule. Nino le serre contre sa joue. Un lampadaire fait un petit tic. Il est prêt, maintenant. On grimpe, avec lui.</t>
+          <t>L'ombre violette touche déjà l'herbe. Le doudou dort dans le bac, tout sablé. Le doudou est. Aniss garde les mains, et attend. Il le veut, ce doudou ? Le doudou est tout sablé. On le tapote. Le sable tombe, un nuage minuscule. Nino le serre contre sa joue. Un lampadaire fait un petit tic. Il est prêt, maintenant. Ils glissent, le doudou entre eux.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -13717,7 +13717,7 @@
 narrateur|Nino le serre contre sa joue.
 narrateur|Un lampadaire fait un petit tic.
 maman|Il est prêt, maintenant.
-enfant-m|On grimpe, avec lui.</t>
+narrateur|Ils glissent, le doudou entre eux.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -14300,12 +14300,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Maintenant le toboggan refroidit. Le ballon rouge coince un barreau. Le ballon va. Aniss ouvre les mains, en bas, et attend. Tu le laisses dire ? Le ballon va tomber. Je suis là. Nino pousse, tout doux. Le rouge atterrit dans les mains d'Aniss. Un lampadaire fait un petit tic. Le chemin est libre. On monte, puis on glisse !</t>
+          <t>Maintenant le toboggan refroidit. Le ballon rouge coince un barreau. Le ballon va. Aniss ouvre les mains, en bas, et attend. Tu le laisses dire ? Le ballon va tomber. Je suis là. Nino pousse, tout doux. Le rouge atterrit dans les mains d'Aniss. Un lampadaire fait un petit tic. Le chemin est libre. Ils montent, puis ça dévale.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Maintenant le toboggan refroidit. Le ballon rouge coince un barreau. Le ballon va. Aniss ouvre les mains, en bas, et attend. Tu le laisses dire ? Le ballon va tomber. Je suis là. Nino pousse, tout doux. Le rouge atterrit dans les mains d'Aniss. Un lampadaire fait un petit tic. Le chemin est libre. On monte, puis on glisse !</t>
+          <t>Maintenant le toboggan refroidit. Le ballon rouge coince un barreau. Le ballon va. Aniss ouvre les mains, en bas, et attend. Tu le laisses dire ? Le ballon va tomber. Je suis là. Nino pousse, tout doux. Le rouge atterrit dans les mains d'Aniss. Un lampadaire fait un petit tic. Le chemin est libre. Ils montent, puis ça dévale.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -14447,7 +14447,7 @@
 narrateur|Le rouge atterrit dans les mains d'Aniss.
 narrateur|Un lampadaire fait un petit tic.
 papa|Le chemin est libre.
-enfant-m|On monte, puis on glisse !</t>
+narrateur|Ils montent, puis ça dévale.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -14659,12 +14659,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>L'ombre violette touche déjà l'herbe. Le seau bleu pend près du haut. Le seau va. Aniss reste un barreau plus bas. On l'écoute, d'accord ? Le seau va nous aider. Je te le tends. Nino pousse le sable, tout lentement. Les grains tombent dans le bleu. Voilà le sable, déjà refroidi, tout fin. La rampe redevient glissante. À nous !</t>
+          <t>L'ombre violette touche déjà l'herbe. Le seau bleu pend près du haut. Le seau va. Aniss reste un barreau plus bas. On l'écoute, d'accord ? Le seau va nous aider. Je te le tends. Nino pousse le sable, tout lentement. Les grains tombent dans le bleu. Voilà le sable, déjà refroidi, tout fin. La rampe redevient glissante. Ils dévalent, le seau à la main.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>L'ombre violette touche déjà l'herbe. Le seau bleu pend près du haut. Le seau va. Aniss reste un barreau plus bas. On l'écoute, d'accord ? Le seau va nous aider. Je te le tends. Nino pousse le sable, tout lentement. Les grains tombent dans le bleu. Voilà le sable, déjà refroidi, tout fin. La rampe redevient glissante. À nous !</t>
+          <t>L'ombre violette touche déjà l'herbe. Le seau bleu pend près du haut. Le seau va. Aniss reste un barreau plus bas. On l'écoute, d'accord ? Le seau va nous aider. Je te le tends. Nino pousse le sable, tout lentement. Les grains tombent dans le bleu. Voilà le sable, déjà refroidi, tout fin. La rampe redevient glissante. Ils dévalent, le seau à la main.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -14806,7 +14806,7 @@
 narrateur|Les grains tombent dans le bleu.
 narrateur|Voilà le sable, déjà refroidi, tout fin.
 maman|La rampe redevient glissante.
-enfant-m|À nous !</t>
+narrateur|Ils dévalent, le seau à la main.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -15018,12 +15018,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>La lumière devient orange, tout doux. Le doudou est coincé sur un barreau. Le doudou va. Aniss ne le prend pas, et attend. Sa phrase n'est pas finie. Le doudou va avec moi. Je te le passe. Nino le glisse sous son bras. Ils montent, barreau après barreau. Maintenant le toboggan refroidit. Vous y êtes, tout en haut. On glisse ensemble !</t>
+          <t>La lumière devient orange, tout doux. Le doudou est coincé sur un barreau. Le doudou va. Aniss ne le prend pas, et attend. Il cherche encore. Le doudou va avec moi. Je te le passe. Nino le glisse sous son bras. Ils montent, barreau après barreau. Maintenant le toboggan refroidit. Vous y êtes, tout en haut. Ils glissent, le doudou au milieu.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>La lumière devient orange, tout doux. Le doudou est coincé sur un barreau. Le doudou va. Aniss ne le prend pas, et attend. Sa phrase n'est pas finie. Le doudou va avec moi. Je te le passe. Nino le glisse sous son bras. Ils montent, barreau après barreau. Maintenant le toboggan refroidit. Vous y êtes, tout en haut. On glisse ensemble !</t>
+          <t>La lumière devient orange, tout doux. Le doudou est coincé sur un barreau. Le doudou va. Aniss ne le prend pas, et attend. Il cherche encore. Le doudou va avec moi. Je te le passe. Nino le glisse sous son bras. Ils montent, barreau après barreau. Maintenant le toboggan refroidit. Vous y êtes, tout en haut. Ils glissent, le doudou au milieu.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -15158,14 +15158,14 @@
 narrateur|Le doudou est coincé sur un barreau.
 copain|Le doudou va.
 narrateur|Aniss ne le prend pas, et attend.
-maman|Sa phrase n'est pas finie.
+maman|Il cherche encore.
 copain|Le doudou va avec moi.
 enfant-m|Je te le passe.
 narrateur|Nino le glisse sous son bras.
 narrateur|Ils montent, barreau après barreau.
 narrateur|Maintenant le toboggan refroidit.
 papa|Vous y êtes, tout en haut.
-enfant-m|On glisse ensemble !</t>
+narrateur|Ils glissent, le doudou au milieu.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -16819,7 +16819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16869,6 +16869,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
